--- a/GearSage-client/rate/excel/spinning_reel_detail.xlsx
+++ b/GearSage-client/rate/excel/spinning_reel_detail.xlsx
@@ -65245,7 +65245,7 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v/>
+        <v>MRED50000</v>
       </c>
       <c r="B719" t="str">
         <v>MRE5000</v>
@@ -65337,7 +65337,7 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v/>
+        <v>MRED50001</v>
       </c>
       <c r="B720" t="str">
         <v>MRE5001</v>

--- a/GearSage-client/rate/excel/spinning_reel_detail.xlsx
+++ b/GearSage-client/rate/excel/spinning_reel_detail.xlsx
@@ -547,10 +547,10 @@
         <v>047472</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U2" t="str">
         <v/>
@@ -578,6 +578,9 @@
       </c>
       <c r="AC2" t="str">
         <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="3">
@@ -636,10 +639,10 @@
         <v>047489</v>
       </c>
       <c r="S3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U3" t="str">
         <v/>
@@ -667,6 +670,9 @@
       </c>
       <c r="AC3" t="str">
         <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="4">
@@ -725,10 +731,10 @@
         <v>047496</v>
       </c>
       <c r="S4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U4" t="str">
         <v/>
@@ -756,6 +762,9 @@
       </c>
       <c r="AC4" t="str">
         <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="5">
@@ -814,10 +823,10 @@
         <v>047502</v>
       </c>
       <c r="S5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U5" t="str">
         <v/>
@@ -845,6 +854,9 @@
       </c>
       <c r="AC5" t="str">
         <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="6">
@@ -903,10 +915,10 @@
         <v>047519</v>
       </c>
       <c r="S6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U6" t="str">
         <v/>
@@ -934,6 +946,9 @@
       </c>
       <c r="AC6" t="str">
         <v/>
+      </c>
+      <c r="AD6" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="7">
@@ -992,10 +1007,10 @@
         <v>047526</v>
       </c>
       <c r="S7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U7" t="str">
         <v/>
@@ -1023,6 +1038,9 @@
       </c>
       <c r="AC7" t="str">
         <v/>
+      </c>
+      <c r="AD7" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="8">
@@ -1081,10 +1099,10 @@
         <v>047533</v>
       </c>
       <c r="S8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U8" t="str">
         <v/>
@@ -1112,6 +1130,9 @@
       </c>
       <c r="AC8" t="str">
         <v/>
+      </c>
+      <c r="AD8" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="9">
@@ -1170,10 +1191,10 @@
         <v>047540</v>
       </c>
       <c r="S9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U9" t="str">
         <v/>
@@ -1201,6 +1222,9 @@
       </c>
       <c r="AC9" t="str">
         <v/>
+      </c>
+      <c r="AD9" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="10">
@@ -1259,10 +1283,10 @@
         <v>047557</v>
       </c>
       <c r="S10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U10" t="str">
         <v/>
@@ -1290,6 +1314,9 @@
       </c>
       <c r="AC10" t="str">
         <v/>
+      </c>
+      <c r="AD10" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="11">
@@ -1348,10 +1375,10 @@
         <v>047564</v>
       </c>
       <c r="S11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U11" t="str">
         <v/>
@@ -1379,6 +1406,9 @@
       </c>
       <c r="AC11" t="str">
         <v/>
+      </c>
+      <c r="AD11" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="12">
@@ -1437,10 +1467,10 @@
         <v>047571</v>
       </c>
       <c r="S12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U12" t="str">
         <v/>
@@ -1468,6 +1498,9 @@
       </c>
       <c r="AC12" t="str">
         <v/>
+      </c>
+      <c r="AD12" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="13">
@@ -1526,10 +1559,10 @@
         <v>047588</v>
       </c>
       <c r="S13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U13" t="str">
         <v/>
@@ -1557,6 +1590,9 @@
       </c>
       <c r="AC13" t="str">
         <v/>
+      </c>
+      <c r="AD13" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="14">
@@ -1615,10 +1651,10 @@
         <v>047595</v>
       </c>
       <c r="S14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U14" t="str">
         <v/>
@@ -1646,6 +1682,9 @@
       </c>
       <c r="AC14" t="str">
         <v/>
+      </c>
+      <c r="AD14" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="15">
@@ -1704,10 +1743,10 @@
         <v>047601</v>
       </c>
       <c r="S15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U15" t="str">
         <v/>
@@ -1735,6 +1774,9 @@
       </c>
       <c r="AC15" t="str">
         <v/>
+      </c>
+      <c r="AD15" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="16">
@@ -1793,10 +1835,10 @@
         <v>047618</v>
       </c>
       <c r="S16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T16" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U16" t="str">
         <v/>
@@ -1824,6 +1866,9 @@
       </c>
       <c r="AC16" t="str">
         <v/>
+      </c>
+      <c r="AD16" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="17">
@@ -1882,10 +1927,10 @@
         <v>047625</v>
       </c>
       <c r="S17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U17" t="str">
         <v/>
@@ -1913,6 +1958,9 @@
       </c>
       <c r="AC17" t="str">
         <v/>
+      </c>
+      <c r="AD17" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="18">
@@ -1971,10 +2019,10 @@
         <v>048059</v>
       </c>
       <c r="S18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U18" t="str">
         <v/>
@@ -2002,6 +2050,9 @@
       </c>
       <c r="AC18" t="str">
         <v/>
+      </c>
+      <c r="AD18" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="19">
@@ -2060,10 +2111,10 @@
         <v>041289</v>
       </c>
       <c r="S19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U19" t="str">
         <v/>
@@ -2091,6 +2142,9 @@
       </c>
       <c r="AC19" t="str">
         <v/>
+      </c>
+      <c r="AD19" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="20">
@@ -2149,10 +2203,10 @@
         <v>040824</v>
       </c>
       <c r="S20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U20" t="str">
         <v/>
@@ -2180,6 +2234,9 @@
       </c>
       <c r="AC20" t="str">
         <v/>
+      </c>
+      <c r="AD20" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="21">
@@ -2238,10 +2295,10 @@
         <v>047793</v>
       </c>
       <c r="S21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U21" t="str">
         <v/>
@@ -2269,6 +2326,9 @@
       </c>
       <c r="AC21" t="str">
         <v/>
+      </c>
+      <c r="AD21" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="22">
@@ -2327,10 +2387,10 @@
         <v>047809</v>
       </c>
       <c r="S22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U22" t="str">
         <v/>
@@ -2358,6 +2418,9 @@
       </c>
       <c r="AC22" t="str">
         <v/>
+      </c>
+      <c r="AD22" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="23">
@@ -2416,10 +2479,10 @@
         <v>047816</v>
       </c>
       <c r="S23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T23" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U23" t="str">
         <v/>
@@ -2447,6 +2510,9 @@
       </c>
       <c r="AC23" t="str">
         <v/>
+      </c>
+      <c r="AD23" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="24">
@@ -2505,10 +2571,10 @@
         <v>047823</v>
       </c>
       <c r="S24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T24" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U24" t="str">
         <v/>
@@ -2536,6 +2602,9 @@
       </c>
       <c r="AC24" t="str">
         <v/>
+      </c>
+      <c r="AD24" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="25">
@@ -2594,10 +2663,10 @@
         <v>043528</v>
       </c>
       <c r="S25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T25" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U25" t="str">
         <v/>
@@ -2625,6 +2694,9 @@
       </c>
       <c r="AC25" t="str">
         <v/>
+      </c>
+      <c r="AD25" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="26">
@@ -2683,10 +2755,10 @@
         <v>043535</v>
       </c>
       <c r="S26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T26" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U26" t="str">
         <v/>
@@ -2714,6 +2786,9 @@
       </c>
       <c r="AC26" t="str">
         <v/>
+      </c>
+      <c r="AD26" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="27">
@@ -2772,10 +2847,10 @@
         <v>043542</v>
       </c>
       <c r="S27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T27" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U27" t="str">
         <v/>
@@ -2803,6 +2878,9 @@
       </c>
       <c r="AC27" t="str">
         <v/>
+      </c>
+      <c r="AD27" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="28">
@@ -2861,10 +2939,10 @@
         <v>043559</v>
       </c>
       <c r="S28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T28" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U28" t="str">
         <v/>
@@ -2892,6 +2970,9 @@
       </c>
       <c r="AC28" t="str">
         <v/>
+      </c>
+      <c r="AD28" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="29">
@@ -2950,10 +3031,10 @@
         <v>043566</v>
       </c>
       <c r="S29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T29" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U29" t="str">
         <v/>
@@ -2981,6 +3062,9 @@
       </c>
       <c r="AC29" t="str">
         <v/>
+      </c>
+      <c r="AD29" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="30">
@@ -3039,10 +3123,10 @@
         <v>044341</v>
       </c>
       <c r="S30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T30" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U30" t="str">
         <v/>
@@ -3070,6 +3154,9 @@
       </c>
       <c r="AC30" t="str">
         <v>20</v>
+      </c>
+      <c r="AD30" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="31">
@@ -3128,10 +3215,10 @@
         <v>044358</v>
       </c>
       <c r="S31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T31" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U31" t="str">
         <v/>
@@ -3159,6 +3246,9 @@
       </c>
       <c r="AC31" t="str">
         <v>20</v>
+      </c>
+      <c r="AD31" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="32">
@@ -3217,10 +3307,10 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T32" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U32" t="str">
         <v/>
@@ -3248,6 +3338,9 @@
       </c>
       <c r="AC32" t="str">
         <v/>
+      </c>
+      <c r="AD32" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="33">
@@ -3306,10 +3399,10 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T33" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U33" t="str">
         <v/>
@@ -3337,6 +3430,9 @@
       </c>
       <c r="AC33" t="str">
         <v/>
+      </c>
+      <c r="AD33" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="34">
@@ -3395,10 +3491,10 @@
         <v>-</v>
       </c>
       <c r="S34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T34" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U34" t="str">
         <v/>
@@ -3426,6 +3522,9 @@
       </c>
       <c r="AC34" t="str">
         <v/>
+      </c>
+      <c r="AD34" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="35">
@@ -3484,10 +3583,10 @@
         <v>043825</v>
       </c>
       <c r="S35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T35" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U35" t="str">
         <v/>
@@ -3515,6 +3614,9 @@
       </c>
       <c r="AC35" t="str">
         <v/>
+      </c>
+      <c r="AD35" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="36">
@@ -3573,10 +3675,10 @@
         <v>043832</v>
       </c>
       <c r="S36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T36" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U36" t="str">
         <v/>
@@ -3604,6 +3706,9 @@
       </c>
       <c r="AC36" t="str">
         <v/>
+      </c>
+      <c r="AD36" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="37">
@@ -3662,10 +3767,10 @@
         <v>043849</v>
       </c>
       <c r="S37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T37" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U37" t="str">
         <v/>
@@ -3693,6 +3798,9 @@
       </c>
       <c r="AC37" t="str">
         <v/>
+      </c>
+      <c r="AD37" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="38">
@@ -3751,10 +3859,10 @@
         <v>043856</v>
       </c>
       <c r="S38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T38" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U38" t="str">
         <v/>
@@ -3782,6 +3890,9 @@
       </c>
       <c r="AC38" t="str">
         <v/>
+      </c>
+      <c r="AD38" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="39">
@@ -3840,10 +3951,10 @@
         <v>043863</v>
       </c>
       <c r="S39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T39" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U39" t="str">
         <v/>
@@ -3871,6 +3982,9 @@
       </c>
       <c r="AC39" t="str">
         <v/>
+      </c>
+      <c r="AD39" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="40">
@@ -3929,10 +4043,10 @@
         <v>-</v>
       </c>
       <c r="S40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T40" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U40" t="str">
         <v/>
@@ -3960,6 +4074,9 @@
       </c>
       <c r="AC40" t="str">
         <v/>
+      </c>
+      <c r="AD40" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="41">
@@ -4018,10 +4135,10 @@
         <v>-</v>
       </c>
       <c r="S41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T41" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U41" t="str">
         <v/>
@@ -4049,6 +4166,9 @@
       </c>
       <c r="AC41" t="str">
         <v/>
+      </c>
+      <c r="AD41" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="42">
@@ -4107,10 +4227,10 @@
         <v>043870</v>
       </c>
       <c r="S42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T42" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U42" t="str">
         <v/>
@@ -4138,6 +4258,9 @@
       </c>
       <c r="AC42" t="str">
         <v/>
+      </c>
+      <c r="AD42" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="43">
@@ -4196,10 +4319,10 @@
         <v>043887</v>
       </c>
       <c r="S43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T43" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U43" t="str">
         <v/>
@@ -4227,6 +4350,9 @@
       </c>
       <c r="AC43" t="str">
         <v/>
+      </c>
+      <c r="AD43" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="44">
@@ -4285,10 +4411,10 @@
         <v>-</v>
       </c>
       <c r="S44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T44" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U44" t="str">
         <v/>
@@ -4316,6 +4442,9 @@
       </c>
       <c r="AC44" t="str">
         <v/>
+      </c>
+      <c r="AD44" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="45">
@@ -4374,10 +4503,10 @@
         <v>043894</v>
       </c>
       <c r="S45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T45" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U45" t="str">
         <v/>
@@ -4405,6 +4534,9 @@
       </c>
       <c r="AC45" t="str">
         <v/>
+      </c>
+      <c r="AD45" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="46">
@@ -4463,10 +4595,10 @@
         <v>043900</v>
       </c>
       <c r="S46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T46" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U46" t="str">
         <v/>
@@ -4494,6 +4626,9 @@
       </c>
       <c r="AC46" t="str">
         <v/>
+      </c>
+      <c r="AD46" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="47">
@@ -4552,10 +4687,10 @@
         <v>043917</v>
       </c>
       <c r="S47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T47" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U47" t="str">
         <v/>
@@ -4583,6 +4718,9 @@
       </c>
       <c r="AC47" t="str">
         <v/>
+      </c>
+      <c r="AD47" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="48">
@@ -4641,10 +4779,10 @@
         <v>043924</v>
       </c>
       <c r="S48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T48" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U48" t="str">
         <v/>
@@ -4672,6 +4810,9 @@
       </c>
       <c r="AC48" t="str">
         <v/>
+      </c>
+      <c r="AD48" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="49">
@@ -4730,10 +4871,10 @@
         <v>043931</v>
       </c>
       <c r="S49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T49" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U49" t="str">
         <v/>
@@ -4761,6 +4902,9 @@
       </c>
       <c r="AC49" t="str">
         <v/>
+      </c>
+      <c r="AD49" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="50">
@@ -4819,10 +4963,10 @@
         <v>043948</v>
       </c>
       <c r="S50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T50" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U50" t="str">
         <v/>
@@ -4850,6 +4994,9 @@
       </c>
       <c r="AC50" t="str">
         <v/>
+      </c>
+      <c r="AD50" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="51">
@@ -4908,10 +5055,10 @@
         <v>043955</v>
       </c>
       <c r="S51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T51" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U51" t="str">
         <v/>
@@ -4939,6 +5086,9 @@
       </c>
       <c r="AC51" t="str">
         <v/>
+      </c>
+      <c r="AD51" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="52">
@@ -4997,10 +5147,10 @@
         <v>043962</v>
       </c>
       <c r="S52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T52" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U52" t="str">
         <v/>
@@ -5028,6 +5178,9 @@
       </c>
       <c r="AC52" t="str">
         <v/>
+      </c>
+      <c r="AD52" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="53">
@@ -5086,10 +5239,10 @@
         <v>043979</v>
       </c>
       <c r="S53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T53" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U53" t="str">
         <v/>
@@ -5117,6 +5270,9 @@
       </c>
       <c r="AC53" t="str">
         <v/>
+      </c>
+      <c r="AD53" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="54">
@@ -5175,10 +5331,10 @@
         <v>-</v>
       </c>
       <c r="S54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T54" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U54" t="str">
         <v/>
@@ -5206,6 +5362,9 @@
       </c>
       <c r="AC54" t="str">
         <v/>
+      </c>
+      <c r="AD54" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="55">
@@ -5264,10 +5423,10 @@
         <v>048202</v>
       </c>
       <c r="S55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T55" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U55" t="str">
         <v/>
@@ -5295,6 +5454,9 @@
       </c>
       <c r="AC55" t="str">
         <v/>
+      </c>
+      <c r="AD55" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="56">
@@ -5353,10 +5515,10 @@
         <v>048219</v>
       </c>
       <c r="S56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T56" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U56" t="str">
         <v/>
@@ -5384,6 +5546,9 @@
       </c>
       <c r="AC56" t="str">
         <v/>
+      </c>
+      <c r="AD56" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="57">
@@ -5442,10 +5607,10 @@
         <v>048226</v>
       </c>
       <c r="S57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T57" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U57" t="str">
         <v/>
@@ -5473,6 +5638,9 @@
       </c>
       <c r="AC57" t="str">
         <v/>
+      </c>
+      <c r="AD57" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="58">
@@ -5531,10 +5699,10 @@
         <v>042217</v>
       </c>
       <c r="S58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T58" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U58" t="str">
         <v/>
@@ -5562,6 +5730,9 @@
       </c>
       <c r="AC58" t="str">
         <v/>
+      </c>
+      <c r="AD58" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="59">
@@ -5620,10 +5791,10 @@
         <v>042224</v>
       </c>
       <c r="S59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T59" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U59" t="str">
         <v/>
@@ -5651,6 +5822,9 @@
       </c>
       <c r="AC59" t="str">
         <v/>
+      </c>
+      <c r="AD59" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="60">
@@ -5709,10 +5883,10 @@
         <v>042231</v>
       </c>
       <c r="S60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T60" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U60" t="str">
         <v/>
@@ -5740,6 +5914,9 @@
       </c>
       <c r="AC60" t="str">
         <v/>
+      </c>
+      <c r="AD60" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="61">
@@ -5798,10 +5975,10 @@
         <v>042248</v>
       </c>
       <c r="S61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T61" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U61" t="str">
         <v/>
@@ -5829,6 +6006,9 @@
       </c>
       <c r="AC61" t="str">
         <v/>
+      </c>
+      <c r="AD61" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="62">
@@ -5887,10 +6067,10 @@
         <v>042255</v>
       </c>
       <c r="S62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T62" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U62" t="str">
         <v/>
@@ -5918,6 +6098,9 @@
       </c>
       <c r="AC62" t="str">
         <v/>
+      </c>
+      <c r="AD62" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="63">
@@ -5976,10 +6159,10 @@
         <v>042262</v>
       </c>
       <c r="S63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T63" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U63" t="str">
         <v/>
@@ -6007,6 +6190,9 @@
       </c>
       <c r="AC63" t="str">
         <v/>
+      </c>
+      <c r="AD63" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="64">
@@ -6065,10 +6251,10 @@
         <v>042279</v>
       </c>
       <c r="S64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T64" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U64" t="str">
         <v/>
@@ -6096,6 +6282,9 @@
       </c>
       <c r="AC64" t="str">
         <v/>
+      </c>
+      <c r="AD64" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="65">
@@ -6154,10 +6343,10 @@
         <v>042286</v>
       </c>
       <c r="S65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T65" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U65" t="str">
         <v/>
@@ -6185,6 +6374,9 @@
       </c>
       <c r="AC65" t="str">
         <v/>
+      </c>
+      <c r="AD65" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="66">
@@ -6243,10 +6435,10 @@
         <v>042293</v>
       </c>
       <c r="S66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T66" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U66" t="str">
         <v/>
@@ -6274,6 +6466,9 @@
       </c>
       <c r="AC66" t="str">
         <v/>
+      </c>
+      <c r="AD66" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="67">
@@ -6332,10 +6527,10 @@
         <v>042309</v>
       </c>
       <c r="S67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T67" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U67" t="str">
         <v/>
@@ -6363,6 +6558,9 @@
       </c>
       <c r="AC67" t="str">
         <v/>
+      </c>
+      <c r="AD67" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="68">
@@ -6421,10 +6619,10 @@
         <v>043511</v>
       </c>
       <c r="S68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T68" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U68" t="str">
         <v/>
@@ -6452,6 +6650,9 @@
       </c>
       <c r="AC68" t="str">
         <v/>
+      </c>
+      <c r="AD68" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="69">
@@ -6510,10 +6711,10 @@
         <v>042316</v>
       </c>
       <c r="S69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T69" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U69" t="str">
         <v/>
@@ -6541,6 +6742,9 @@
       </c>
       <c r="AC69" t="str">
         <v/>
+      </c>
+      <c r="AD69" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="70">
@@ -6599,10 +6803,10 @@
         <v/>
       </c>
       <c r="S70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T70" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U70" t="str">
         <v/>
@@ -6630,6 +6834,9 @@
       </c>
       <c r="AC70" t="str">
         <v/>
+      </c>
+      <c r="AD70" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="71">
@@ -6688,10 +6895,10 @@
         <v/>
       </c>
       <c r="S71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T71" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U71" t="str">
         <v/>
@@ -6719,6 +6926,9 @@
       </c>
       <c r="AC71" t="str">
         <v/>
+      </c>
+      <c r="AD71" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="72">
@@ -6777,10 +6987,10 @@
         <v/>
       </c>
       <c r="S72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T72" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U72" t="str">
         <v/>
@@ -6808,6 +7018,9 @@
       </c>
       <c r="AC72" t="str">
         <v/>
+      </c>
+      <c r="AD72" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="73">
@@ -6866,10 +7079,10 @@
         <v>049025</v>
       </c>
       <c r="S73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T73" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U73" t="str">
         <v/>
@@ -6897,6 +7110,9 @@
       </c>
       <c r="AC73" t="str">
         <v/>
+      </c>
+      <c r="AD73" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="74">
@@ -6955,10 +7171,10 @@
         <v>049032</v>
       </c>
       <c r="S74" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T74" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U74" t="str">
         <v/>
@@ -6986,6 +7202,9 @@
       </c>
       <c r="AC74" t="str">
         <v/>
+      </c>
+      <c r="AD74" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="75">
@@ -7044,10 +7263,10 @@
         <v>049049</v>
       </c>
       <c r="S75" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T75" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U75" t="str">
         <v/>
@@ -7075,6 +7294,9 @@
       </c>
       <c r="AC75" t="str">
         <v/>
+      </c>
+      <c r="AD75" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="76">
@@ -7133,10 +7355,10 @@
         <v>049056</v>
       </c>
       <c r="S76" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T76" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U76" t="str">
         <v/>
@@ -7164,6 +7386,9 @@
       </c>
       <c r="AC76" t="str">
         <v/>
+      </c>
+      <c r="AD76" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="77">
@@ -7222,10 +7447,10 @@
         <v>043429</v>
       </c>
       <c r="S77" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T77" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U77" t="str">
         <v/>
@@ -7253,6 +7478,9 @@
       </c>
       <c r="AC77" t="str">
         <v/>
+      </c>
+      <c r="AD77" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="78">
@@ -7311,10 +7539,10 @@
         <v>047243</v>
       </c>
       <c r="S78" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T78" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U78" t="str">
         <v/>
@@ -7342,6 +7570,9 @@
       </c>
       <c r="AC78" t="str">
         <v>20</v>
+      </c>
+      <c r="AD78" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="79">
@@ -7400,10 +7631,10 @@
         <v>047250</v>
       </c>
       <c r="S79" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T79" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U79" t="str">
         <v/>
@@ -7431,6 +7662,9 @@
       </c>
       <c r="AC79" t="str">
         <v>20</v>
+      </c>
+      <c r="AD79" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="80">
@@ -7489,10 +7723,10 @@
         <v>047267</v>
       </c>
       <c r="S80" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T80" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U80" t="str">
         <v/>
@@ -7520,6 +7754,9 @@
       </c>
       <c r="AC80" t="str">
         <v>-</v>
+      </c>
+      <c r="AD80" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="81">
@@ -7578,10 +7815,10 @@
         <v>049247</v>
       </c>
       <c r="S81" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T81" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U81" t="str">
         <v/>
@@ -7609,6 +7846,9 @@
       </c>
       <c r="AC81" t="str">
         <v/>
+      </c>
+      <c r="AD81" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="82">
@@ -7667,10 +7907,10 @@
         <v>049254</v>
       </c>
       <c r="S82" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T82" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U82" t="str">
         <v/>
@@ -7698,6 +7938,9 @@
       </c>
       <c r="AC82" t="str">
         <v/>
+      </c>
+      <c r="AD82" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="83">
@@ -7756,10 +7999,10 @@
         <v>049261</v>
       </c>
       <c r="S83" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T83" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U83" t="str">
         <v/>
@@ -7787,6 +8030,9 @@
       </c>
       <c r="AC83" t="str">
         <v/>
+      </c>
+      <c r="AD83" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="84">
@@ -7845,10 +8091,10 @@
         <v>049278</v>
       </c>
       <c r="S84" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T84" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U84" t="str">
         <v/>
@@ -7876,6 +8122,9 @@
       </c>
       <c r="AC84" t="str">
         <v/>
+      </c>
+      <c r="AD84" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="85">
@@ -7934,10 +8183,10 @@
         <v>049285</v>
       </c>
       <c r="S85" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T85" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U85" t="str">
         <v/>
@@ -7965,6 +8214,9 @@
       </c>
       <c r="AC85" t="str">
         <v/>
+      </c>
+      <c r="AD85" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="86">
@@ -8023,10 +8275,10 @@
         <v>049292</v>
       </c>
       <c r="S86" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T86" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U86" t="str">
         <v/>
@@ -8054,6 +8306,9 @@
       </c>
       <c r="AC86" t="str">
         <v/>
+      </c>
+      <c r="AD86" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="87">
@@ -8112,10 +8367,10 @@
         <v>049308</v>
       </c>
       <c r="S87" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T87" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U87" t="str">
         <v/>
@@ -8143,6 +8398,9 @@
       </c>
       <c r="AC87" t="str">
         <v/>
+      </c>
+      <c r="AD87" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="88">
@@ -8201,10 +8459,10 @@
         <v>049315</v>
       </c>
       <c r="S88" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T88" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U88" t="str">
         <v/>
@@ -8232,6 +8490,9 @@
       </c>
       <c r="AC88" t="str">
         <v/>
+      </c>
+      <c r="AD88" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="89">
@@ -8290,10 +8551,10 @@
         <v>045225</v>
       </c>
       <c r="S89" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T89" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U89" t="str">
         <v/>
@@ -8321,6 +8582,9 @@
       </c>
       <c r="AC89" t="str">
         <v/>
+      </c>
+      <c r="AD89" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="90">
@@ -8379,10 +8643,10 @@
         <v>045232</v>
       </c>
       <c r="S90" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T90" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U90" t="str">
         <v/>
@@ -8410,6 +8674,9 @@
       </c>
       <c r="AC90" t="str">
         <v/>
+      </c>
+      <c r="AD90" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="91">
@@ -8468,10 +8735,10 @@
         <v>045249</v>
       </c>
       <c r="S91" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T91" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U91" t="str">
         <v/>
@@ -8499,6 +8766,9 @@
       </c>
       <c r="AC91" t="str">
         <v/>
+      </c>
+      <c r="AD91" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="92">
@@ -8557,10 +8827,10 @@
         <v>045256</v>
       </c>
       <c r="S92" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T92" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U92" t="str">
         <v/>
@@ -8588,6 +8858,9 @@
       </c>
       <c r="AC92" t="str">
         <v/>
+      </c>
+      <c r="AD92" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="93">
@@ -8646,10 +8919,10 @@
         <v>045263</v>
       </c>
       <c r="S93" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T93" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U93" t="str">
         <v/>
@@ -8677,6 +8950,9 @@
       </c>
       <c r="AC93" t="str">
         <v/>
+      </c>
+      <c r="AD93" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="94">
@@ -8735,10 +9011,10 @@
         <v>045270</v>
       </c>
       <c r="S94" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T94" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U94" t="str">
         <v/>
@@ -8766,6 +9042,9 @@
       </c>
       <c r="AC94" t="str">
         <v/>
+      </c>
+      <c r="AD94" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="95">
@@ -8824,10 +9103,10 @@
         <v>045287</v>
       </c>
       <c r="S95" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T95" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U95" t="str">
         <v/>
@@ -8855,6 +9134,9 @@
       </c>
       <c r="AC95" t="str">
         <v/>
+      </c>
+      <c r="AD95" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="96">
@@ -8913,10 +9195,10 @@
         <v>045294</v>
       </c>
       <c r="S96" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T96" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U96" t="str">
         <v/>
@@ -8944,6 +9226,9 @@
       </c>
       <c r="AC96" t="str">
         <v/>
+      </c>
+      <c r="AD96" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="97">
@@ -9002,10 +9287,10 @@
         <v>045300</v>
       </c>
       <c r="S97" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T97" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U97" t="str">
         <v/>
@@ -9033,6 +9318,9 @@
       </c>
       <c r="AC97" t="str">
         <v/>
+      </c>
+      <c r="AD97" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="98">
@@ -9091,10 +9379,10 @@
         <v>045317</v>
       </c>
       <c r="S98" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T98" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U98" t="str">
         <v/>
@@ -9122,6 +9410,9 @@
       </c>
       <c r="AC98" t="str">
         <v/>
+      </c>
+      <c r="AD98" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="99">
@@ -9180,10 +9471,10 @@
         <v>045324</v>
       </c>
       <c r="S99" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T99" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U99" t="str">
         <v/>
@@ -9211,6 +9502,9 @@
       </c>
       <c r="AC99" t="str">
         <v/>
+      </c>
+      <c r="AD99" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="100">
@@ -9269,10 +9563,10 @@
         <v>045331</v>
       </c>
       <c r="S100" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T100" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U100" t="str">
         <v/>
@@ -9300,6 +9594,9 @@
       </c>
       <c r="AC100" t="str">
         <v/>
+      </c>
+      <c r="AD100" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="101">
@@ -9358,10 +9655,10 @@
         <v>045348</v>
       </c>
       <c r="S101" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T101" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U101" t="str">
         <v/>
@@ -9389,6 +9686,9 @@
       </c>
       <c r="AC101" t="str">
         <v/>
+      </c>
+      <c r="AD101" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="102">
@@ -9447,10 +9747,10 @@
         <v>045355</v>
       </c>
       <c r="S102" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T102" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U102" t="str">
         <v/>
@@ -9478,6 +9778,9 @@
       </c>
       <c r="AC102" t="str">
         <v/>
+      </c>
+      <c r="AD102" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="103">
@@ -9536,10 +9839,10 @@
         <v>045362</v>
       </c>
       <c r="S103" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T103" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U103" t="str">
         <v/>
@@ -9567,6 +9870,9 @@
       </c>
       <c r="AC103" t="str">
         <v/>
+      </c>
+      <c r="AD103" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="104">
@@ -9625,10 +9931,10 @@
         <v/>
       </c>
       <c r="S104" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T104" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U104" t="str">
         <v/>
@@ -9656,6 +9962,9 @@
       </c>
       <c r="AC104" t="str">
         <v/>
+      </c>
+      <c r="AD104" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="105">
@@ -9714,10 +10023,10 @@
         <v/>
       </c>
       <c r="S105" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T105" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U105" t="str">
         <v/>
@@ -9745,6 +10054,9 @@
       </c>
       <c r="AC105" t="str">
         <v/>
+      </c>
+      <c r="AD105" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="106">
@@ -9803,10 +10115,10 @@
         <v/>
       </c>
       <c r="S106" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T106" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U106" t="str">
         <v/>
@@ -9834,6 +10146,9 @@
       </c>
       <c r="AC106" t="str">
         <v/>
+      </c>
+      <c r="AD106" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="107">
@@ -9892,10 +10207,10 @@
         <v/>
       </c>
       <c r="S107" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T107" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U107" t="str">
         <v/>
@@ -9923,6 +10238,9 @@
       </c>
       <c r="AC107" t="str">
         <v/>
+      </c>
+      <c r="AD107" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="108">
@@ -9981,10 +10299,10 @@
         <v/>
       </c>
       <c r="S108" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T108" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U108" t="str">
         <v/>
@@ -10012,6 +10330,9 @@
       </c>
       <c r="AC108" t="str">
         <v/>
+      </c>
+      <c r="AD108" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="109">
@@ -10070,10 +10391,10 @@
         <v/>
       </c>
       <c r="S109" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T109" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U109" t="str">
         <v/>
@@ -10101,6 +10422,9 @@
       </c>
       <c r="AC109" t="str">
         <v/>
+      </c>
+      <c r="AD109" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="110">
@@ -10159,10 +10483,10 @@
         <v/>
       </c>
       <c r="S110" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T110" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U110" t="str">
         <v/>
@@ -10190,6 +10514,9 @@
       </c>
       <c r="AC110" t="str">
         <v/>
+      </c>
+      <c r="AD110" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="111">
@@ -10248,10 +10575,10 @@
         <v/>
       </c>
       <c r="S111" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T111" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U111" t="str">
         <v/>
@@ -10279,6 +10606,9 @@
       </c>
       <c r="AC111" t="str">
         <v/>
+      </c>
+      <c r="AD111" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="112">
@@ -10337,10 +10667,10 @@
         <v>044884</v>
       </c>
       <c r="S112" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T112" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U112" t="str">
         <v/>
@@ -10368,6 +10698,9 @@
       </c>
       <c r="AC112" t="str">
         <v/>
+      </c>
+      <c r="AD112" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="113">
@@ -10426,10 +10759,10 @@
         <v>044891</v>
       </c>
       <c r="S113" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T113" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U113" t="str">
         <v/>
@@ -10457,6 +10790,9 @@
       </c>
       <c r="AC113" t="str">
         <v/>
+      </c>
+      <c r="AD113" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="114">
@@ -10515,10 +10851,10 @@
         <v>044907</v>
       </c>
       <c r="S114" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T114" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U114" t="str">
         <v/>
@@ -10546,6 +10882,9 @@
       </c>
       <c r="AC114" t="str">
         <v/>
+      </c>
+      <c r="AD114" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="115">
@@ -10604,10 +10943,10 @@
         <v>044914</v>
       </c>
       <c r="S115" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T115" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U115" t="str">
         <v/>
@@ -10635,6 +10974,9 @@
       </c>
       <c r="AC115" t="str">
         <v/>
+      </c>
+      <c r="AD115" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="116">
@@ -10693,10 +11035,10 @@
         <v>044921</v>
       </c>
       <c r="S116" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T116" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U116" t="str">
         <v/>
@@ -10724,6 +11066,9 @@
       </c>
       <c r="AC116" t="str">
         <v/>
+      </c>
+      <c r="AD116" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="117">
@@ -10782,10 +11127,10 @@
         <v>044938</v>
       </c>
       <c r="S117" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T117" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U117" t="str">
         <v/>
@@ -10813,6 +11158,9 @@
       </c>
       <c r="AC117" t="str">
         <v/>
+      </c>
+      <c r="AD117" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="118">
@@ -10871,10 +11219,10 @@
         <v>044945</v>
       </c>
       <c r="S118" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T118" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U118" t="str">
         <v/>
@@ -10902,6 +11250,9 @@
       </c>
       <c r="AC118" t="str">
         <v/>
+      </c>
+      <c r="AD118" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="119">
@@ -10960,10 +11311,10 @@
         <v>039392</v>
       </c>
       <c r="S119" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T119" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U119" t="str">
         <v/>
@@ -10991,6 +11342,9 @@
       </c>
       <c r="AC119" t="str">
         <v/>
+      </c>
+      <c r="AD119" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="120">
@@ -11049,10 +11403,10 @@
         <v>039408</v>
       </c>
       <c r="S120" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T120" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U120" t="str">
         <v/>
@@ -11080,6 +11434,9 @@
       </c>
       <c r="AC120" t="str">
         <v/>
+      </c>
+      <c r="AD120" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="121">
@@ -11138,10 +11495,10 @@
         <v>039415</v>
       </c>
       <c r="S121" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T121" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U121" t="str">
         <v/>
@@ -11169,6 +11526,9 @@
       </c>
       <c r="AC121" t="str">
         <v/>
+      </c>
+      <c r="AD121" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="122">
@@ -11227,10 +11587,10 @@
         <v>046765</v>
       </c>
       <c r="S122" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T122" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U122" t="str">
         <v/>
@@ -11258,6 +11618,9 @@
       </c>
       <c r="AC122" t="str">
         <v/>
+      </c>
+      <c r="AD122" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="123">
@@ -11316,10 +11679,10 @@
         <v>046772</v>
       </c>
       <c r="S123" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T123" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U123" t="str">
         <v/>
@@ -11347,6 +11710,9 @@
       </c>
       <c r="AC123" t="str">
         <v/>
+      </c>
+      <c r="AD123" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="124">
@@ -11405,10 +11771,10 @@
         <v>049216</v>
       </c>
       <c r="S124" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T124" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U124" t="str">
         <v/>
@@ -11436,6 +11802,9 @@
       </c>
       <c r="AC124" t="str">
         <v/>
+      </c>
+      <c r="AD124" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="125">
@@ -11494,10 +11863,10 @@
         <v>-</v>
       </c>
       <c r="S125" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T125" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U125" t="str">
         <v/>
@@ -11525,6 +11894,9 @@
       </c>
       <c r="AC125" t="str">
         <v/>
+      </c>
+      <c r="AD125" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="126">
@@ -11583,10 +11955,10 @@
         <v>046789</v>
       </c>
       <c r="S126" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T126" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U126" t="str">
         <v/>
@@ -11614,6 +11986,9 @@
       </c>
       <c r="AC126" t="str">
         <v/>
+      </c>
+      <c r="AD126" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="127">
@@ -11672,10 +12047,10 @@
         <v>046796</v>
       </c>
       <c r="S127" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T127" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U127" t="str">
         <v/>
@@ -11703,6 +12078,9 @@
       </c>
       <c r="AC127" t="str">
         <v/>
+      </c>
+      <c r="AD127" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="128">
@@ -11761,10 +12139,10 @@
         <v>046802</v>
       </c>
       <c r="S128" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T128" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U128" t="str">
         <v/>
@@ -11792,6 +12170,9 @@
       </c>
       <c r="AC128" t="str">
         <v/>
+      </c>
+      <c r="AD128" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="129">
@@ -11850,10 +12231,10 @@
         <v>046819</v>
       </c>
       <c r="S129" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T129" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U129" t="str">
         <v/>
@@ -11881,6 +12262,9 @@
       </c>
       <c r="AC129" t="str">
         <v/>
+      </c>
+      <c r="AD129" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="130">
@@ -11939,10 +12323,10 @@
         <v>046826</v>
       </c>
       <c r="S130" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T130" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U130" t="str">
         <v/>
@@ -11970,6 +12354,9 @@
       </c>
       <c r="AC130" t="str">
         <v/>
+      </c>
+      <c r="AD130" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="131">
@@ -12028,10 +12415,10 @@
         <v>046833</v>
       </c>
       <c r="S131" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T131" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U131" t="str">
         <v/>
@@ -12059,6 +12446,9 @@
       </c>
       <c r="AC131" t="str">
         <v/>
+      </c>
+      <c r="AD131" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="132">
@@ -12117,10 +12507,10 @@
         <v>046840</v>
       </c>
       <c r="S132" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T132" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U132" t="str">
         <v/>
@@ -12148,6 +12538,9 @@
       </c>
       <c r="AC132" t="str">
         <v/>
+      </c>
+      <c r="AD132" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="133">
@@ -12206,10 +12599,10 @@
         <v>046857</v>
       </c>
       <c r="S133" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T133" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U133" t="str">
         <v/>
@@ -12237,6 +12630,9 @@
       </c>
       <c r="AC133" t="str">
         <v/>
+      </c>
+      <c r="AD133" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="134">
@@ -12295,10 +12691,10 @@
         <v>046864</v>
       </c>
       <c r="S134" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T134" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U134" t="str">
         <v/>
@@ -12326,6 +12722,9 @@
       </c>
       <c r="AC134" t="str">
         <v/>
+      </c>
+      <c r="AD134" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="135">
@@ -12384,10 +12783,10 @@
         <v>046871</v>
       </c>
       <c r="S135" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T135" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U135" t="str">
         <v/>
@@ -12415,6 +12814,9 @@
       </c>
       <c r="AC135" t="str">
         <v/>
+      </c>
+      <c r="AD135" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="136">
@@ -12473,10 +12875,10 @@
         <v>046888</v>
       </c>
       <c r="S136" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T136" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U136" t="str">
         <v/>
@@ -12504,6 +12906,9 @@
       </c>
       <c r="AC136" t="str">
         <v/>
+      </c>
+      <c r="AD136" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="137">
@@ -12562,10 +12967,10 @@
         <v>047885</v>
       </c>
       <c r="S137" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T137" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U137" t="str">
         <v/>
@@ -12593,6 +12998,9 @@
       </c>
       <c r="AC137" t="str">
         <v/>
+      </c>
+      <c r="AD137" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="138">
@@ -12651,10 +13059,10 @@
         <v>047892</v>
       </c>
       <c r="S138" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T138" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U138" t="str">
         <v/>
@@ -12682,6 +13090,9 @@
       </c>
       <c r="AC138" t="str">
         <v/>
+      </c>
+      <c r="AD138" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="139">
@@ -12740,10 +13151,10 @@
         <v>047908</v>
       </c>
       <c r="S139" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T139" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U139" t="str">
         <v/>
@@ -12771,6 +13182,9 @@
       </c>
       <c r="AC139" t="str">
         <v/>
+      </c>
+      <c r="AD139" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="140">
@@ -12829,10 +13243,10 @@
         <v>047915</v>
       </c>
       <c r="S140" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T140" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U140" t="str">
         <v/>
@@ -12860,6 +13274,9 @@
       </c>
       <c r="AC140" t="str">
         <v/>
+      </c>
+      <c r="AD140" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="141">
@@ -12918,10 +13335,10 @@
         <v>047922</v>
       </c>
       <c r="S141" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T141" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U141" t="str">
         <v/>
@@ -12949,6 +13366,9 @@
       </c>
       <c r="AC141" t="str">
         <v/>
+      </c>
+      <c r="AD141" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="142">
@@ -13007,10 +13427,10 @@
         <v>047939</v>
       </c>
       <c r="S142" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T142" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U142" t="str">
         <v/>
@@ -13038,6 +13458,9 @@
       </c>
       <c r="AC142" t="str">
         <v/>
+      </c>
+      <c r="AD142" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="143">
@@ -13096,10 +13519,10 @@
         <v>046239</v>
       </c>
       <c r="S143" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T143" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U143" t="str">
         <v/>
@@ -13127,6 +13550,9 @@
       </c>
       <c r="AC143" t="str">
         <v/>
+      </c>
+      <c r="AD143" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="144">
@@ -13185,10 +13611,10 @@
         <v>046246</v>
       </c>
       <c r="S144" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T144" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U144" t="str">
         <v/>
@@ -13216,6 +13642,9 @@
       </c>
       <c r="AC144" t="str">
         <v/>
+      </c>
+      <c r="AD144" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="145">
@@ -13274,10 +13703,10 @@
         <v>046253</v>
       </c>
       <c r="S145" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T145" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U145" t="str">
         <v/>
@@ -13305,6 +13734,9 @@
       </c>
       <c r="AC145" t="str">
         <v/>
+      </c>
+      <c r="AD145" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="146">
@@ -13363,10 +13795,10 @@
         <v>046086</v>
       </c>
       <c r="S146" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T146" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U146" t="str">
         <v/>
@@ -13394,6 +13826,9 @@
       </c>
       <c r="AC146" t="str">
         <v/>
+      </c>
+      <c r="AD146" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="147">
@@ -13452,10 +13887,10 @@
         <v>046093</v>
       </c>
       <c r="S147" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T147" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U147" t="str">
         <v/>
@@ -13483,6 +13918,9 @@
       </c>
       <c r="AC147" t="str">
         <v/>
+      </c>
+      <c r="AD147" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="148">
@@ -13541,10 +13979,10 @@
         <v>046109</v>
       </c>
       <c r="S148" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T148" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U148" t="str">
         <v/>
@@ -13572,6 +14010,9 @@
       </c>
       <c r="AC148" t="str">
         <v/>
+      </c>
+      <c r="AD148" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="149">
@@ -13630,10 +14071,10 @@
         <v/>
       </c>
       <c r="S149" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T149" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U149" t="str">
         <v/>
@@ -13661,6 +14102,9 @@
       </c>
       <c r="AC149" t="str">
         <v/>
+      </c>
+      <c r="AD149" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="150">
@@ -13719,10 +14163,10 @@
         <v/>
       </c>
       <c r="S150" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T150" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U150" t="str">
         <v/>
@@ -13750,6 +14194,9 @@
       </c>
       <c r="AC150" t="str">
         <v/>
+      </c>
+      <c r="AD150" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="151">
@@ -13808,10 +14255,10 @@
         <v>042781</v>
       </c>
       <c r="S151" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T151" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U151" t="str">
         <v/>
@@ -13839,6 +14286,9 @@
       </c>
       <c r="AC151" t="str">
         <v/>
+      </c>
+      <c r="AD151" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="152">
@@ -13897,10 +14347,10 @@
         <v>042798</v>
       </c>
       <c r="S152" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T152" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U152" t="str">
         <v/>
@@ -13928,6 +14378,9 @@
       </c>
       <c r="AC152" t="str">
         <v/>
+      </c>
+      <c r="AD152" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="153">
@@ -13986,10 +14439,10 @@
         <v>042804</v>
       </c>
       <c r="S153" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T153" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U153" t="str">
         <v/>
@@ -14017,6 +14470,9 @@
       </c>
       <c r="AC153" t="str">
         <v/>
+      </c>
+      <c r="AD153" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="154">
@@ -14075,10 +14531,10 @@
         <v>042811</v>
       </c>
       <c r="S154" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T154" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U154" t="str">
         <v/>
@@ -14106,6 +14562,9 @@
       </c>
       <c r="AC154" t="str">
         <v/>
+      </c>
+      <c r="AD154" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="155">
@@ -14164,10 +14623,10 @@
         <v>045003</v>
       </c>
       <c r="S155" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T155" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U155" t="str">
         <v/>
@@ -14195,6 +14654,9 @@
       </c>
       <c r="AC155" t="str">
         <v/>
+      </c>
+      <c r="AD155" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="156">
@@ -14253,10 +14715,10 @@
         <v>046154</v>
       </c>
       <c r="S156" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T156" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U156" t="str">
         <v/>
@@ -14284,6 +14746,9 @@
       </c>
       <c r="AC156" t="str">
         <v/>
+      </c>
+      <c r="AD156" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="157">
@@ -14342,10 +14807,10 @@
         <v>046161</v>
       </c>
       <c r="S157" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T157" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U157" t="str">
         <v/>
@@ -14373,6 +14838,9 @@
       </c>
       <c r="AC157" t="str">
         <v/>
+      </c>
+      <c r="AD157" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="158">
@@ -14431,10 +14899,10 @@
         <v>046178</v>
       </c>
       <c r="S158" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T158" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U158" t="str">
         <v/>
@@ -14462,6 +14930,9 @@
       </c>
       <c r="AC158" t="str">
         <v/>
+      </c>
+      <c r="AD158" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="159">
@@ -14520,10 +14991,10 @@
         <v>046185</v>
       </c>
       <c r="S159" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T159" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U159" t="str">
         <v/>
@@ -14551,6 +15022,9 @@
       </c>
       <c r="AC159" t="str">
         <v/>
+      </c>
+      <c r="AD159" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="160">
@@ -14609,10 +15083,10 @@
         <v>045676</v>
       </c>
       <c r="S160" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T160" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U160" t="str">
         <v/>
@@ -14640,6 +15114,9 @@
       </c>
       <c r="AC160" t="str">
         <v/>
+      </c>
+      <c r="AD160" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="161">
@@ -14698,10 +15175,10 @@
         <v>048905</v>
       </c>
       <c r="S161" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T161" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U161" t="str">
         <v/>
@@ -14729,6 +15206,9 @@
       </c>
       <c r="AC161" t="str">
         <v/>
+      </c>
+      <c r="AD161" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="162">
@@ -14787,10 +15267,10 @@
         <v>048912</v>
       </c>
       <c r="S162" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T162" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U162" t="str">
         <v/>
@@ -14818,6 +15298,9 @@
       </c>
       <c r="AC162" t="str">
         <v/>
+      </c>
+      <c r="AD162" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="163">
@@ -14876,10 +15359,10 @@
         <v>048929</v>
       </c>
       <c r="S163" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T163" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U163" t="str">
         <v/>
@@ -14907,6 +15390,9 @@
       </c>
       <c r="AC163" t="str">
         <v/>
+      </c>
+      <c r="AD163" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="164">
@@ -14965,10 +15451,10 @@
         <v>048936</v>
       </c>
       <c r="S164" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T164" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U164" t="str">
         <v/>
@@ -14996,6 +15482,9 @@
       </c>
       <c r="AC164" t="str">
         <v/>
+      </c>
+      <c r="AD164" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="165">
@@ -15054,10 +15543,10 @@
         <v>048943</v>
       </c>
       <c r="S165" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T165" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U165" t="str">
         <v/>
@@ -15085,6 +15574,9 @@
       </c>
       <c r="AC165" t="str">
         <v/>
+      </c>
+      <c r="AD165" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="166">
@@ -15143,10 +15635,10 @@
         <v>047373</v>
       </c>
       <c r="S166" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T166" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U166" t="str">
         <v/>
@@ -15174,6 +15666,9 @@
       </c>
       <c r="AC166" t="str">
         <v/>
+      </c>
+      <c r="AD166" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="167">
@@ -15232,10 +15727,10 @@
         <v>047380</v>
       </c>
       <c r="S167" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T167" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U167" t="str">
         <v/>
@@ -15263,6 +15758,9 @@
       </c>
       <c r="AC167" t="str">
         <v/>
+      </c>
+      <c r="AD167" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="168">
@@ -15321,10 +15819,10 @@
         <v>047397</v>
       </c>
       <c r="S168" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T168" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U168" t="str">
         <v/>
@@ -15352,6 +15850,9 @@
       </c>
       <c r="AC168" t="str">
         <v/>
+      </c>
+      <c r="AD168" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="169">
@@ -15410,10 +15911,10 @@
         <v>047403</v>
       </c>
       <c r="S169" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T169" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U169" t="str">
         <v/>
@@ -15441,6 +15942,9 @@
       </c>
       <c r="AC169" t="str">
         <v/>
+      </c>
+      <c r="AD169" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="170">
@@ -15499,10 +16003,10 @@
         <v>047410</v>
       </c>
       <c r="S170" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T170" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U170" t="str">
         <v/>
@@ -15530,6 +16034,9 @@
       </c>
       <c r="AC170" t="str">
         <v/>
+      </c>
+      <c r="AD170" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="171">
@@ -15588,10 +16095,10 @@
         <v>047427</v>
       </c>
       <c r="S171" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T171" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U171" t="str">
         <v/>
@@ -15619,6 +16126,9 @@
       </c>
       <c r="AC171" t="str">
         <v/>
+      </c>
+      <c r="AD171" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="172">
@@ -15677,10 +16187,10 @@
         <v>047434</v>
       </c>
       <c r="S172" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T172" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U172" t="str">
         <v/>
@@ -15708,6 +16218,9 @@
       </c>
       <c r="AC172" t="str">
         <v/>
+      </c>
+      <c r="AD172" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="173">
@@ -15766,10 +16279,10 @@
         <v>047441</v>
       </c>
       <c r="S173" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T173" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U173" t="str">
         <v/>
@@ -15797,6 +16310,9 @@
       </c>
       <c r="AC173" t="str">
         <v/>
+      </c>
+      <c r="AD173" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="174">
@@ -15855,10 +16371,10 @@
         <v>047458</v>
       </c>
       <c r="S174" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T174" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U174" t="str">
         <v/>
@@ -15886,6 +16402,9 @@
       </c>
       <c r="AC174" t="str">
         <v/>
+      </c>
+      <c r="AD174" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="175">
@@ -15944,10 +16463,10 @@
         <v/>
       </c>
       <c r="S175" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T175" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U175" t="str">
         <v/>
@@ -15975,6 +16494,9 @@
       </c>
       <c r="AC175" t="str">
         <v/>
+      </c>
+      <c r="AD175" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="176">
@@ -16033,10 +16555,10 @@
         <v/>
       </c>
       <c r="S176" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T176" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U176" t="str">
         <v/>
@@ -16064,6 +16586,9 @@
       </c>
       <c r="AC176" t="str">
         <v/>
+      </c>
+      <c r="AD176" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="177">
@@ -16122,10 +16647,10 @@
         <v/>
       </c>
       <c r="S177" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T177" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U177" t="str">
         <v/>
@@ -16153,6 +16678,9 @@
       </c>
       <c r="AC177" t="str">
         <v/>
+      </c>
+      <c r="AD177" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="178">
@@ -16211,10 +16739,10 @@
         <v/>
       </c>
       <c r="S178" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T178" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U178" t="str">
         <v/>
@@ -16242,6 +16770,9 @@
       </c>
       <c r="AC178" t="str">
         <v/>
+      </c>
+      <c r="AD178" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="179">
@@ -16300,10 +16831,10 @@
         <v/>
       </c>
       <c r="S179" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T179" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U179" t="str">
         <v/>
@@ -16331,6 +16862,9 @@
       </c>
       <c r="AC179" t="str">
         <v/>
+      </c>
+      <c r="AD179" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="180">
@@ -16389,10 +16923,10 @@
         <v/>
       </c>
       <c r="S180" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T180" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U180" t="str">
         <v/>
@@ -16420,6 +16954,9 @@
       </c>
       <c r="AC180" t="str">
         <v/>
+      </c>
+      <c r="AD180" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="181">
@@ -16478,10 +17015,10 @@
         <v/>
       </c>
       <c r="S181" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T181" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U181" t="str">
         <v/>
@@ -16509,6 +17046,9 @@
       </c>
       <c r="AC181" t="str">
         <v/>
+      </c>
+      <c r="AD181" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="182">
@@ -16567,10 +17107,10 @@
         <v>048950</v>
       </c>
       <c r="S182" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T182" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U182" t="str">
         <v/>
@@ -16598,6 +17138,9 @@
       </c>
       <c r="AC182" t="str">
         <v/>
+      </c>
+      <c r="AD182" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="183">
@@ -16656,10 +17199,10 @@
         <v>048967</v>
       </c>
       <c r="S183" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T183" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U183" t="str">
         <v/>
@@ -16687,6 +17230,9 @@
       </c>
       <c r="AC183" t="str">
         <v/>
+      </c>
+      <c r="AD183" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="184">
@@ -16745,10 +17291,10 @@
         <v>048974</v>
       </c>
       <c r="S184" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T184" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U184" t="str">
         <v/>
@@ -16776,6 +17322,9 @@
       </c>
       <c r="AC184" t="str">
         <v/>
+      </c>
+      <c r="AD184" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="185">
@@ -16834,10 +17383,10 @@
         <v>048981</v>
       </c>
       <c r="S185" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T185" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U185" t="str">
         <v/>
@@ -16865,6 +17414,9 @@
       </c>
       <c r="AC185" t="str">
         <v/>
+      </c>
+      <c r="AD185" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="186">
@@ -16923,10 +17475,10 @@
         <v>046550</v>
       </c>
       <c r="S186" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T186" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U186" t="str">
         <v/>
@@ -16954,6 +17506,9 @@
       </c>
       <c r="AC186" t="str">
         <v/>
+      </c>
+      <c r="AD186" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="187">
@@ -17012,10 +17567,10 @@
         <v>046567</v>
       </c>
       <c r="S187" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T187" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U187" t="str">
         <v/>
@@ -17043,6 +17598,9 @@
       </c>
       <c r="AC187" t="str">
         <v/>
+      </c>
+      <c r="AD187" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="188">
@@ -17101,10 +17659,10 @@
         <v>046048</v>
       </c>
       <c r="S188" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T188" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U188" t="str">
         <v/>
@@ -17132,6 +17690,9 @@
       </c>
       <c r="AC188" t="str">
         <v/>
+      </c>
+      <c r="AD188" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="189">
@@ -17190,10 +17751,10 @@
         <v>046055</v>
       </c>
       <c r="S189" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T189" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U189" t="str">
         <v/>
@@ -17221,6 +17782,9 @@
       </c>
       <c r="AC189" t="str">
         <v/>
+      </c>
+      <c r="AD189" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="190">
@@ -17279,10 +17843,10 @@
         <v>046062</v>
       </c>
       <c r="S190" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T190" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U190" t="str">
         <v/>
@@ -17310,6 +17874,9 @@
       </c>
       <c r="AC190" t="str">
         <v/>
+      </c>
+      <c r="AD190" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="191">
@@ -17368,10 +17935,10 @@
         <v>046079</v>
       </c>
       <c r="S191" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T191" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U191" t="str">
         <v/>
@@ -17399,6 +17966,9 @@
       </c>
       <c r="AC191" t="str">
         <v/>
+      </c>
+      <c r="AD191" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="192">
@@ -17457,10 +18027,10 @@
         <v>032713</v>
       </c>
       <c r="S192" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T192" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U192" t="str">
         <v/>
@@ -17488,6 +18058,9 @@
       </c>
       <c r="AC192" t="str">
         <v/>
+      </c>
+      <c r="AD192" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="193">
@@ -17546,10 +18119,10 @@
         <v>032720</v>
       </c>
       <c r="S193" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T193" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U193" t="str">
         <v/>
@@ -17577,6 +18150,9 @@
       </c>
       <c r="AC193" t="str">
         <v/>
+      </c>
+      <c r="AD193" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="194">
@@ -17635,10 +18211,10 @@
         <v>032737</v>
       </c>
       <c r="S194" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T194" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U194" t="str">
         <v/>
@@ -17666,6 +18242,9 @@
       </c>
       <c r="AC194" t="str">
         <v/>
+      </c>
+      <c r="AD194" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="195">
@@ -17724,10 +18303,10 @@
         <v>032744</v>
       </c>
       <c r="S195" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T195" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U195" t="str">
         <v/>
@@ -17755,6 +18334,9 @@
       </c>
       <c r="AC195" t="str">
         <v/>
+      </c>
+      <c r="AD195" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="196">
@@ -17813,10 +18395,10 @@
         <v>048424</v>
       </c>
       <c r="S196" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T196" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U196" t="str">
         <v/>
@@ -17844,6 +18426,9 @@
       </c>
       <c r="AC196" t="str">
         <v/>
+      </c>
+      <c r="AD196" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="197">
@@ -17902,10 +18487,10 @@
         <v>048431</v>
       </c>
       <c r="S197" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T197" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U197" t="str">
         <v/>
@@ -17933,6 +18518,9 @@
       </c>
       <c r="AC197" t="str">
         <v/>
+      </c>
+      <c r="AD197" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="198">
@@ -17991,10 +18579,10 @@
         <v>048448</v>
       </c>
       <c r="S198" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T198" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U198" t="str">
         <v/>
@@ -18022,6 +18610,9 @@
       </c>
       <c r="AC198" t="str">
         <v/>
+      </c>
+      <c r="AD198" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="199">
@@ -18080,10 +18671,10 @@
         <v>048455</v>
       </c>
       <c r="S199" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T199" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U199" t="str">
         <v/>
@@ -18111,6 +18702,9 @@
       </c>
       <c r="AC199" t="str">
         <v/>
+      </c>
+      <c r="AD199" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="200">
@@ -18169,10 +18763,10 @@
         <v>044297</v>
       </c>
       <c r="S200" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T200" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U200" t="str">
         <v/>
@@ -18200,6 +18794,9 @@
       </c>
       <c r="AC200" t="str">
         <v/>
+      </c>
+      <c r="AD200" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="201">
@@ -18258,10 +18855,10 @@
         <v/>
       </c>
       <c r="S201" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T201" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U201" t="str">
         <v/>
@@ -18289,6 +18886,9 @@
       </c>
       <c r="AC201" t="str">
         <v/>
+      </c>
+      <c r="AD201" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="202">
@@ -18347,10 +18947,10 @@
         <v/>
       </c>
       <c r="S202" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T202" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U202" t="str">
         <v/>
@@ -18378,6 +18978,9 @@
       </c>
       <c r="AC202" t="str">
         <v/>
+      </c>
+      <c r="AD202" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="203">
@@ -18436,10 +19039,10 @@
         <v>048288</v>
       </c>
       <c r="S203" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T203" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U203" t="str">
         <v/>
@@ -18467,6 +19070,9 @@
       </c>
       <c r="AC203" t="str">
         <v>20</v>
+      </c>
+      <c r="AD203" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="204">
@@ -18525,10 +19131,10 @@
         <v>048295</v>
       </c>
       <c r="S204" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T204" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U204" t="str">
         <v/>
@@ -18556,6 +19162,9 @@
       </c>
       <c r="AC204" t="str">
         <v>20</v>
+      </c>
+      <c r="AD204" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="205">
@@ -18614,10 +19223,10 @@
         <v>048301</v>
       </c>
       <c r="S205" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T205" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U205" t="str">
         <v/>
@@ -18645,6 +19254,9 @@
       </c>
       <c r="AC205" t="str">
         <v>-</v>
+      </c>
+      <c r="AD205" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="206">
@@ -18703,10 +19315,10 @@
         <v>046307</v>
       </c>
       <c r="S206" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T206" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U206" t="str">
         <v/>
@@ -18734,6 +19346,9 @@
       </c>
       <c r="AC206" t="str">
         <v/>
+      </c>
+      <c r="AD206" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="207">
@@ -18792,10 +19407,10 @@
         <v>046314</v>
       </c>
       <c r="S207" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T207" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U207" t="str">
         <v/>
@@ -18823,6 +19438,9 @@
       </c>
       <c r="AC207" t="str">
         <v/>
+      </c>
+      <c r="AD207" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="208">
@@ -18881,10 +19499,10 @@
         <v>046321</v>
       </c>
       <c r="S208" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T208" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U208" t="str">
         <v/>
@@ -18912,6 +19530,9 @@
       </c>
       <c r="AC208" t="str">
         <v/>
+      </c>
+      <c r="AD208" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="209">
@@ -18970,10 +19591,10 @@
         <v>046338</v>
       </c>
       <c r="S209" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T209" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U209" t="str">
         <v/>
@@ -19001,6 +19622,9 @@
       </c>
       <c r="AC209" t="str">
         <v/>
+      </c>
+      <c r="AD209" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="210">
@@ -19059,10 +19683,10 @@
         <v>-</v>
       </c>
       <c r="S210" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T210" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U210" t="str">
         <v/>
@@ -19090,6 +19714,9 @@
       </c>
       <c r="AC210" t="str">
         <v/>
+      </c>
+      <c r="AD210" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="211">
@@ -19148,10 +19775,10 @@
         <v>047014</v>
       </c>
       <c r="S211" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T211" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U211" t="str">
         <v/>
@@ -19179,6 +19806,9 @@
       </c>
       <c r="AC211" t="str">
         <v/>
+      </c>
+      <c r="AD211" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="212">
@@ -19237,10 +19867,10 @@
         <v>047021</v>
       </c>
       <c r="S212" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T212" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U212" t="str">
         <v/>
@@ -19268,6 +19898,9 @@
       </c>
       <c r="AC212" t="str">
         <v/>
+      </c>
+      <c r="AD212" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="213">
@@ -19326,10 +19959,10 @@
         <v>-</v>
       </c>
       <c r="S213" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T213" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U213" t="str">
         <v/>
@@ -19357,6 +19990,9 @@
       </c>
       <c r="AC213" t="str">
         <v/>
+      </c>
+      <c r="AD213" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="214">
@@ -19415,10 +20051,10 @@
         <v>047038</v>
       </c>
       <c r="S214" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T214" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U214" t="str">
         <v/>
@@ -19446,6 +20082,9 @@
       </c>
       <c r="AC214" t="str">
         <v/>
+      </c>
+      <c r="AD214" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="215">
@@ -19504,10 +20143,10 @@
         <v>047045</v>
       </c>
       <c r="S215" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T215" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U215" t="str">
         <v/>
@@ -19535,6 +20174,9 @@
       </c>
       <c r="AC215" t="str">
         <v/>
+      </c>
+      <c r="AD215" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="216">
@@ -19593,10 +20235,10 @@
         <v>047052</v>
       </c>
       <c r="S216" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T216" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U216" t="str">
         <v/>
@@ -19624,6 +20266,9 @@
       </c>
       <c r="AC216" t="str">
         <v/>
+      </c>
+      <c r="AD216" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="217">
@@ -19682,10 +20327,10 @@
         <v>047069</v>
       </c>
       <c r="S217" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T217" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U217" t="str">
         <v/>
@@ -19713,6 +20358,9 @@
       </c>
       <c r="AC217" t="str">
         <v/>
+      </c>
+      <c r="AD217" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="218">
@@ -19771,10 +20419,10 @@
         <v>-</v>
       </c>
       <c r="S218" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T218" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U218" t="str">
         <v/>
@@ -19802,6 +20450,9 @@
       </c>
       <c r="AC218" t="str">
         <v/>
+      </c>
+      <c r="AD218" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="219">
@@ -19860,10 +20511,10 @@
         <v>-</v>
       </c>
       <c r="S219" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T219" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U219" t="str">
         <v/>
@@ -19891,6 +20542,9 @@
       </c>
       <c r="AC219" t="str">
         <v/>
+      </c>
+      <c r="AD219" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="220">
@@ -19949,10 +20603,10 @@
         <v>047090</v>
       </c>
       <c r="S220" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T220" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U220" t="str">
         <v/>
@@ -19980,6 +20634,9 @@
       </c>
       <c r="AC220" t="str">
         <v/>
+      </c>
+      <c r="AD220" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="221">
@@ -20038,10 +20695,10 @@
         <v>-</v>
       </c>
       <c r="S221" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T221" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U221" t="str">
         <v/>
@@ -20069,6 +20726,9 @@
       </c>
       <c r="AC221" t="str">
         <v/>
+      </c>
+      <c r="AD221" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="222">
@@ -20127,10 +20787,10 @@
         <v>047076</v>
       </c>
       <c r="S222" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T222" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U222" t="str">
         <v/>
@@ -20158,6 +20818,9 @@
       </c>
       <c r="AC222" t="str">
         <v/>
+      </c>
+      <c r="AD222" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="223">
@@ -20216,10 +20879,10 @@
         <v>047083</v>
       </c>
       <c r="S223" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T223" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U223" t="str">
         <v/>
@@ -20247,6 +20910,9 @@
       </c>
       <c r="AC223" t="str">
         <v/>
+      </c>
+      <c r="AD223" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="224">
@@ -20305,10 +20971,10 @@
         <v>047106</v>
       </c>
       <c r="S224" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T224" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U224" t="str">
         <v/>
@@ -20336,6 +21002,9 @@
       </c>
       <c r="AC224" t="str">
         <v/>
+      </c>
+      <c r="AD224" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="225">
@@ -20394,10 +21063,10 @@
         <v>-</v>
       </c>
       <c r="S225" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T225" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U225" t="str">
         <v/>
@@ -20425,6 +21094,9 @@
       </c>
       <c r="AC225" t="str">
         <v/>
+      </c>
+      <c r="AD225" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="226">
@@ -20483,10 +21155,10 @@
         <v>047113</v>
       </c>
       <c r="S226" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T226" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U226" t="str">
         <v/>
@@ -20514,6 +21186,9 @@
       </c>
       <c r="AC226" t="str">
         <v/>
+      </c>
+      <c r="AD226" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="227">
@@ -20572,10 +21247,10 @@
         <v>047120</v>
       </c>
       <c r="S227" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T227" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U227" t="str">
         <v/>
@@ -20603,6 +21278,9 @@
       </c>
       <c r="AC227" t="str">
         <v/>
+      </c>
+      <c r="AD227" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="228">
@@ -20661,10 +21339,10 @@
         <v>047137</v>
       </c>
       <c r="S228" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T228" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U228" t="str">
         <v/>
@@ -20692,6 +21370,9 @@
       </c>
       <c r="AC228" t="str">
         <v/>
+      </c>
+      <c r="AD228" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="229">
@@ -20750,10 +21431,10 @@
         <v/>
       </c>
       <c r="S229" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T229" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U229" t="str">
         <v/>
@@ -20781,6 +21462,9 @@
       </c>
       <c r="AC229" t="str">
         <v/>
+      </c>
+      <c r="AD229" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="230">
@@ -20839,10 +21523,10 @@
         <v/>
       </c>
       <c r="S230" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T230" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U230" t="str">
         <v/>
@@ -20870,6 +21554,9 @@
       </c>
       <c r="AC230" t="str">
         <v/>
+      </c>
+      <c r="AD230" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="231">
@@ -20928,10 +21615,10 @@
         <v>046192</v>
       </c>
       <c r="S231" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T231" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U231" t="str">
         <v/>
@@ -20959,6 +21646,9 @@
       </c>
       <c r="AC231" t="str">
         <v/>
+      </c>
+      <c r="AD231" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="232">
@@ -21017,10 +21707,10 @@
         <v>046208</v>
       </c>
       <c r="S232" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T232" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U232" t="str">
         <v/>
@@ -21048,6 +21738,9 @@
       </c>
       <c r="AC232" t="str">
         <v/>
+      </c>
+      <c r="AD232" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="233">
@@ -21106,10 +21799,10 @@
         <v>046215</v>
       </c>
       <c r="S233" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T233" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U233" t="str">
         <v/>
@@ -21137,6 +21830,9 @@
       </c>
       <c r="AC233" t="str">
         <v/>
+      </c>
+      <c r="AD233" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="234">
@@ -21195,10 +21891,10 @@
         <v>046222</v>
       </c>
       <c r="S234" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T234" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U234" t="str">
         <v/>
@@ -21226,6 +21922,9 @@
       </c>
       <c r="AC234" t="str">
         <v/>
+      </c>
+      <c r="AD234" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="235">
@@ -21284,10 +21983,10 @@
         <v>-</v>
       </c>
       <c r="S235" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T235" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U235" t="str">
         <v/>
@@ -21315,6 +22014,9 @@
       </c>
       <c r="AC235" t="str">
         <v/>
+      </c>
+      <c r="AD235" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="236">
@@ -21373,10 +22075,10 @@
         <v>-</v>
       </c>
       <c r="S236" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T236" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U236" t="str">
         <v/>
@@ -21404,6 +22106,9 @@
       </c>
       <c r="AC236" t="str">
         <v/>
+      </c>
+      <c r="AD236" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="237">
@@ -21462,10 +22167,10 @@
         <v>-</v>
       </c>
       <c r="S237" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T237" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U237" t="str">
         <v/>
@@ -21493,6 +22198,9 @@
       </c>
       <c r="AC237" t="str">
         <v/>
+      </c>
+      <c r="AD237" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="238">
@@ -21551,10 +22259,10 @@
         <v>-</v>
       </c>
       <c r="S238" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T238" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U238" t="str">
         <v/>
@@ -21582,6 +22290,9 @@
       </c>
       <c r="AC238" t="str">
         <v/>
+      </c>
+      <c r="AD238" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="239">
@@ -21640,10 +22351,10 @@
         <v>-</v>
       </c>
       <c r="S239" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T239" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U239" t="str">
         <v/>
@@ -21671,6 +22382,9 @@
       </c>
       <c r="AC239" t="str">
         <v/>
+      </c>
+      <c r="AD239" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="240">
@@ -21729,10 +22443,10 @@
         <v>043610</v>
       </c>
       <c r="S240" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T240" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U240" t="str">
         <v/>
@@ -21760,6 +22474,9 @@
       </c>
       <c r="AC240" t="str">
         <v/>
+      </c>
+      <c r="AD240" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="241">
@@ -21818,10 +22535,10 @@
         <v>043627</v>
       </c>
       <c r="S241" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T241" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U241" t="str">
         <v/>
@@ -21849,6 +22566,9 @@
       </c>
       <c r="AC241" t="str">
         <v/>
+      </c>
+      <c r="AD241" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="242">
@@ -21907,10 +22627,10 @@
         <v>043634</v>
       </c>
       <c r="S242" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T242" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U242" t="str">
         <v/>
@@ -21938,6 +22658,9 @@
       </c>
       <c r="AC242" t="str">
         <v/>
+      </c>
+      <c r="AD242" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="243">
@@ -21996,10 +22719,10 @@
         <v>043641</v>
       </c>
       <c r="S243" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T243" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U243" t="str">
         <v/>
@@ -22027,6 +22750,9 @@
       </c>
       <c r="AC243" t="str">
         <v/>
+      </c>
+      <c r="AD243" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="244">
@@ -22085,10 +22811,10 @@
         <v>043658</v>
       </c>
       <c r="S244" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T244" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U244" t="str">
         <v/>
@@ -22116,6 +22842,9 @@
       </c>
       <c r="AC244" t="str">
         <v/>
+      </c>
+      <c r="AD244" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="245">
@@ -22174,10 +22903,10 @@
         <v/>
       </c>
       <c r="S245" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T245" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U245" t="str">
         <v/>
@@ -22205,6 +22934,9 @@
       </c>
       <c r="AC245" t="str">
         <v/>
+      </c>
+      <c r="AD245" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="246">
@@ -22263,10 +22995,10 @@
         <v>-</v>
       </c>
       <c r="S246" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T246" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U246" t="str">
         <v/>
@@ -22294,6 +23026,9 @@
       </c>
       <c r="AC246" t="str">
         <v/>
+      </c>
+      <c r="AD246" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="247">
@@ -22352,10 +23087,10 @@
         <v>-</v>
       </c>
       <c r="S247" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T247" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U247" t="str">
         <v/>
@@ -22383,6 +23118,9 @@
       </c>
       <c r="AC247" t="str">
         <v/>
+      </c>
+      <c r="AD247" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="248">
@@ -22441,10 +23179,10 @@
         <v>-</v>
       </c>
       <c r="S248" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T248" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U248" t="str">
         <v/>
@@ -22472,6 +23210,9 @@
       </c>
       <c r="AC248" t="str">
         <v/>
+      </c>
+      <c r="AD248" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="249">
@@ -22530,10 +23271,10 @@
         <v>045782</v>
       </c>
       <c r="S249" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T249" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U249" t="str">
         <v/>
@@ -22561,6 +23302,9 @@
       </c>
       <c r="AC249" t="str">
         <v/>
+      </c>
+      <c r="AD249" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="250">
@@ -22619,10 +23363,10 @@
         <v>045799</v>
       </c>
       <c r="S250" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T250" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U250" t="str">
         <v/>
@@ -22650,6 +23394,9 @@
       </c>
       <c r="AC250" t="str">
         <v/>
+      </c>
+      <c r="AD250" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="251">
@@ -22708,10 +23455,10 @@
         <v>045805</v>
       </c>
       <c r="S251" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T251" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U251" t="str">
         <v/>
@@ -22739,6 +23486,9 @@
       </c>
       <c r="AC251" t="str">
         <v/>
+      </c>
+      <c r="AD251" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="252">
@@ -22797,10 +23547,10 @@
         <v>045812</v>
       </c>
       <c r="S252" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T252" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U252" t="str">
         <v/>
@@ -22828,6 +23578,9 @@
       </c>
       <c r="AC252" t="str">
         <v/>
+      </c>
+      <c r="AD252" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="253">
@@ -22886,10 +23639,10 @@
         <v>-</v>
       </c>
       <c r="S253" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T253" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U253" t="str">
         <v/>
@@ -22917,6 +23670,9 @@
       </c>
       <c r="AC253" t="str">
         <v/>
+      </c>
+      <c r="AD253" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="254">
@@ -22975,10 +23731,10 @@
         <v>-</v>
       </c>
       <c r="S254" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T254" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U254" t="str">
         <v/>
@@ -23006,6 +23762,9 @@
       </c>
       <c r="AC254" t="str">
         <v/>
+      </c>
+      <c r="AD254" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="255">
@@ -23064,10 +23823,10 @@
         <v>045829</v>
       </c>
       <c r="S255" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T255" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U255" t="str">
         <v/>
@@ -23095,6 +23854,9 @@
       </c>
       <c r="AC255" t="str">
         <v/>
+      </c>
+      <c r="AD255" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="256">
@@ -23153,10 +23915,10 @@
         <v>045836</v>
       </c>
       <c r="S256" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T256" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U256" t="str">
         <v/>
@@ -23184,6 +23946,9 @@
       </c>
       <c r="AC256" t="str">
         <v/>
+      </c>
+      <c r="AD256" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="257">
@@ -23242,10 +24007,10 @@
         <v>045843</v>
       </c>
       <c r="S257" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T257" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U257" t="str">
         <v/>
@@ -23273,6 +24038,9 @@
       </c>
       <c r="AC257" t="str">
         <v/>
+      </c>
+      <c r="AD257" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="258">
@@ -23331,10 +24099,10 @@
         <v>045850</v>
       </c>
       <c r="S258" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T258" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U258" t="str">
         <v/>
@@ -23362,6 +24130,9 @@
       </c>
       <c r="AC258" t="str">
         <v/>
+      </c>
+      <c r="AD258" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="259">
@@ -23420,10 +24191,10 @@
         <v>045867</v>
       </c>
       <c r="S259" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T259" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U259" t="str">
         <v/>
@@ -23451,6 +24222,9 @@
       </c>
       <c r="AC259" t="str">
         <v/>
+      </c>
+      <c r="AD259" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="260">
@@ -23509,10 +24283,10 @@
         <v>045874</v>
       </c>
       <c r="S260" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T260" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U260" t="str">
         <v/>
@@ -23540,6 +24314,9 @@
       </c>
       <c r="AC260" t="str">
         <v/>
+      </c>
+      <c r="AD260" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="261">
@@ -23598,10 +24375,10 @@
         <v>045881</v>
       </c>
       <c r="S261" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T261" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U261" t="str">
         <v/>
@@ -23629,6 +24406,9 @@
       </c>
       <c r="AC261" t="str">
         <v/>
+      </c>
+      <c r="AD261" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="262">
@@ -23687,10 +24467,10 @@
         <v>045898</v>
       </c>
       <c r="S262" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T262" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U262" t="str">
         <v/>
@@ -23718,6 +24498,9 @@
       </c>
       <c r="AC262" t="str">
         <v/>
+      </c>
+      <c r="AD262" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="263">
@@ -23776,10 +24559,10 @@
         <v>045904</v>
       </c>
       <c r="S263" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T263" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U263" t="str">
         <v/>
@@ -23807,6 +24590,9 @@
       </c>
       <c r="AC263" t="str">
         <v/>
+      </c>
+      <c r="AD263" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="264">
@@ -23865,10 +24651,10 @@
         <v>045911</v>
       </c>
       <c r="S264" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T264" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U264" t="str">
         <v/>
@@ -23896,6 +24682,9 @@
       </c>
       <c r="AC264" t="str">
         <v/>
+      </c>
+      <c r="AD264" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="265">
@@ -23954,10 +24743,10 @@
         <v>032522</v>
       </c>
       <c r="S265" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T265" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U265" t="str">
         <v/>
@@ -23985,6 +24774,9 @@
       </c>
       <c r="AC265" t="str">
         <v>20</v>
+      </c>
+      <c r="AD265" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="266">
@@ -24043,10 +24835,10 @@
         <v>032539</v>
       </c>
       <c r="S266" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T266" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U266" t="str">
         <v/>
@@ -24074,6 +24866,9 @@
       </c>
       <c r="AC266" t="str">
         <v>20</v>
+      </c>
+      <c r="AD266" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="267">
@@ -24132,10 +24927,10 @@
         <v>032690</v>
       </c>
       <c r="S267" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T267" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U267" t="str">
         <v/>
@@ -24163,6 +24958,9 @@
       </c>
       <c r="AC267" t="str">
         <v>12</v>
+      </c>
+      <c r="AD267" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="268">
@@ -24221,10 +25019,10 @@
         <v>032706</v>
       </c>
       <c r="S268" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T268" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U268" t="str">
         <v/>
@@ -24252,6 +25050,9 @@
       </c>
       <c r="AC268" t="str">
         <v>12</v>
+      </c>
+      <c r="AD268" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="269">
@@ -24310,10 +25111,10 @@
         <v/>
       </c>
       <c r="S269" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T269" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U269" t="str">
         <v/>
@@ -24341,6 +25142,9 @@
       </c>
       <c r="AC269" t="str">
         <v/>
+      </c>
+      <c r="AD269" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="270">
@@ -24399,10 +25203,10 @@
         <v>045553</v>
       </c>
       <c r="S270" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T270" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U270" t="str">
         <v/>
@@ -24430,6 +25234,9 @@
       </c>
       <c r="AC270" t="str">
         <v/>
+      </c>
+      <c r="AD270" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="271">
@@ -24488,10 +25295,10 @@
         <v>045560</v>
       </c>
       <c r="S271" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T271" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U271" t="str">
         <v/>
@@ -24519,6 +25326,9 @@
       </c>
       <c r="AC271" t="str">
         <v/>
+      </c>
+      <c r="AD271" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="272">
@@ -24577,10 +25387,10 @@
         <v>045577</v>
       </c>
       <c r="S272" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T272" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U272" t="str">
         <v/>
@@ -24608,6 +25418,9 @@
       </c>
       <c r="AC272" t="str">
         <v/>
+      </c>
+      <c r="AD272" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="273">
@@ -24666,10 +25479,10 @@
         <v>045584</v>
       </c>
       <c r="S273" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T273" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U273" t="str">
         <v/>
@@ -24697,6 +25510,9 @@
       </c>
       <c r="AC273" t="str">
         <v/>
+      </c>
+      <c r="AD273" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="274">
@@ -24755,10 +25571,10 @@
         <v>047205</v>
       </c>
       <c r="S274" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T274" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U274" t="str">
         <v/>
@@ -24786,6 +25602,9 @@
       </c>
       <c r="AC274" t="str">
         <v/>
+      </c>
+      <c r="AD274" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="275">
@@ -24844,10 +25663,10 @@
         <v>047212</v>
       </c>
       <c r="S275" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T275" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U275" t="str">
         <v/>
@@ -24875,6 +25694,9 @@
       </c>
       <c r="AC275" t="str">
         <v/>
+      </c>
+      <c r="AD275" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="276">
@@ -24933,10 +25755,10 @@
         <v>047229</v>
       </c>
       <c r="S276" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T276" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U276" t="str">
         <v/>
@@ -24964,6 +25786,9 @@
       </c>
       <c r="AC276" t="str">
         <v/>
+      </c>
+      <c r="AD276" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="277">
@@ -25022,10 +25847,10 @@
         <v>047236</v>
       </c>
       <c r="S277" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T277" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U277" t="str">
         <v/>
@@ -25053,6 +25878,9 @@
       </c>
       <c r="AC277" t="str">
         <v/>
+      </c>
+      <c r="AD277" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="278">
@@ -25111,10 +25939,10 @@
         <v/>
       </c>
       <c r="S278" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T278" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U278" t="str">
         <v/>
@@ -25142,6 +25970,9 @@
       </c>
       <c r="AC278" t="str">
         <v/>
+      </c>
+      <c r="AD278" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="279">
@@ -25200,10 +26031,10 @@
         <v/>
       </c>
       <c r="S279" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T279" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U279" t="str">
         <v/>
@@ -25231,6 +26062,9 @@
       </c>
       <c r="AC279" t="str">
         <v/>
+      </c>
+      <c r="AD279" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="280">
@@ -25289,10 +26123,10 @@
         <v/>
       </c>
       <c r="S280" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T280" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U280" t="str">
         <v/>
@@ -25320,6 +26154,9 @@
       </c>
       <c r="AC280" t="str">
         <v/>
+      </c>
+      <c r="AD280" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="281">
@@ -25378,10 +26215,10 @@
         <v>-</v>
       </c>
       <c r="S281" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T281" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U281" t="str">
         <v/>
@@ -25409,6 +26246,9 @@
       </c>
       <c r="AC281" t="str">
         <v/>
+      </c>
+      <c r="AD281" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="282">
@@ -25467,10 +26307,10 @@
         <v>-</v>
       </c>
       <c r="S282" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T282" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U282" t="str">
         <v/>
@@ -25498,6 +26338,9 @@
       </c>
       <c r="AC282" t="str">
         <v/>
+      </c>
+      <c r="AD282" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="283">
@@ -25556,10 +26399,10 @@
         <v>047946</v>
       </c>
       <c r="S283" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T283" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U283" t="str">
         <v/>
@@ -25587,6 +26430,9 @@
       </c>
       <c r="AC283" t="str">
         <v/>
+      </c>
+      <c r="AD283" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="284">
@@ -25645,10 +26491,10 @@
         <v>047953</v>
       </c>
       <c r="S284" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T284" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U284" t="str">
         <v/>
@@ -25676,6 +26522,9 @@
       </c>
       <c r="AC284" t="str">
         <v/>
+      </c>
+      <c r="AD284" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="285">
@@ -25734,10 +26583,10 @@
         <v>047960</v>
       </c>
       <c r="S285" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T285" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U285" t="str">
         <v/>
@@ -25765,6 +26614,9 @@
       </c>
       <c r="AC285" t="str">
         <v/>
+      </c>
+      <c r="AD285" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="286">
@@ -25823,10 +26675,10 @@
         <v>047977</v>
       </c>
       <c r="S286" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T286" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U286" t="str">
         <v/>
@@ -25854,6 +26706,9 @@
       </c>
       <c r="AC286" t="str">
         <v/>
+      </c>
+      <c r="AD286" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="287">
@@ -25912,10 +26767,10 @@
         <v>-</v>
       </c>
       <c r="S287" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T287" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U287" t="str">
         <v/>
@@ -25943,6 +26798,9 @@
       </c>
       <c r="AC287" t="str">
         <v/>
+      </c>
+      <c r="AD287" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="288">
@@ -26001,10 +26859,10 @@
         <v>047984</v>
       </c>
       <c r="S288" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T288" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U288" t="str">
         <v/>
@@ -26032,6 +26890,9 @@
       </c>
       <c r="AC288" t="str">
         <v/>
+      </c>
+      <c r="AD288" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="289">
@@ -26090,10 +26951,10 @@
         <v>047991</v>
       </c>
       <c r="S289" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T289" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U289" t="str">
         <v/>
@@ -26121,6 +26982,9 @@
       </c>
       <c r="AC289" t="str">
         <v/>
+      </c>
+      <c r="AD289" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="290">
@@ -26179,10 +27043,10 @@
         <v>048004</v>
       </c>
       <c r="S290" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T290" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U290" t="str">
         <v/>
@@ -26210,6 +27074,9 @@
       </c>
       <c r="AC290" t="str">
         <v/>
+      </c>
+      <c r="AD290" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="291">
@@ -26268,10 +27135,10 @@
         <v>048011</v>
       </c>
       <c r="S291" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T291" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U291" t="str">
         <v/>
@@ -26299,6 +27166,9 @@
       </c>
       <c r="AC291" t="str">
         <v/>
+      </c>
+      <c r="AD291" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="292">
@@ -26357,10 +27227,10 @@
         <v>048028</v>
       </c>
       <c r="S292" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T292" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U292" t="str">
         <v/>
@@ -26388,6 +27258,9 @@
       </c>
       <c r="AC292" t="str">
         <v/>
+      </c>
+      <c r="AD292" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="293">
@@ -26446,10 +27319,10 @@
         <v>048035</v>
       </c>
       <c r="S293" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T293" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U293" t="str">
         <v/>
@@ -26477,6 +27350,9 @@
       </c>
       <c r="AC293" t="str">
         <v/>
+      </c>
+      <c r="AD293" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="294">
@@ -26535,10 +27411,10 @@
         <v>048042</v>
       </c>
       <c r="S294" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T294" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U294" t="str">
         <v/>
@@ -26566,6 +27442,9 @@
       </c>
       <c r="AC294" t="str">
         <v/>
+      </c>
+      <c r="AD294" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="295">
@@ -26624,10 +27503,10 @@
         <v>045737</v>
       </c>
       <c r="S295" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T295" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U295" t="str">
         <v/>
@@ -26655,6 +27534,9 @@
       </c>
       <c r="AC295" t="str">
         <v/>
+      </c>
+      <c r="AD295" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="296">
@@ -26713,10 +27595,10 @@
         <v>045744</v>
       </c>
       <c r="S296" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T296" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U296" t="str">
         <v/>
@@ -26744,6 +27626,9 @@
       </c>
       <c r="AC296" t="str">
         <v/>
+      </c>
+      <c r="AD296" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="297">
@@ -26802,10 +27687,10 @@
         <v>045751</v>
       </c>
       <c r="S297" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T297" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U297" t="str">
         <v/>
@@ -26833,6 +27718,9 @@
       </c>
       <c r="AC297" t="str">
         <v/>
+      </c>
+      <c r="AD297" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="298">
@@ -26891,10 +27779,10 @@
         <v/>
       </c>
       <c r="S298" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T298" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U298" t="str">
         <v/>
@@ -26922,6 +27810,9 @@
       </c>
       <c r="AC298" t="str">
         <v/>
+      </c>
+      <c r="AD298" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="299">
@@ -26980,10 +27871,10 @@
         <v/>
       </c>
       <c r="S299" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T299" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U299" t="str">
         <v/>
@@ -27011,6 +27902,9 @@
       </c>
       <c r="AC299" t="str">
         <v/>
+      </c>
+      <c r="AD299" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="300">
@@ -27069,10 +27963,10 @@
         <v/>
       </c>
       <c r="S300" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T300" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U300" t="str">
         <v/>
@@ -27100,6 +27994,9 @@
       </c>
       <c r="AC300" t="str">
         <v/>
+      </c>
+      <c r="AD300" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="301">
@@ -27158,10 +28055,10 @@
         <v/>
       </c>
       <c r="S301" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T301" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U301" t="str">
         <v/>
@@ -27189,6 +28086,9 @@
       </c>
       <c r="AC301" t="str">
         <v/>
+      </c>
+      <c r="AD301" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="302">
@@ -27247,10 +28147,10 @@
         <v/>
       </c>
       <c r="S302" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T302" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U302" t="str">
         <v/>
@@ -27278,6 +28178,9 @@
       </c>
       <c r="AC302" t="str">
         <v/>
+      </c>
+      <c r="AD302" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="303">
@@ -27336,10 +28239,10 @@
         <v>-</v>
       </c>
       <c r="S303" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T303" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U303" t="str">
         <v/>
@@ -27367,6 +28270,9 @@
       </c>
       <c r="AC303" t="str">
         <v/>
+      </c>
+      <c r="AD303" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="304">
@@ -27425,10 +28331,10 @@
         <v>041333</v>
       </c>
       <c r="S304" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T304" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U304" t="str">
         <v/>
@@ -27456,6 +28362,9 @@
       </c>
       <c r="AC304" t="str">
         <v/>
+      </c>
+      <c r="AD304" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="305">
@@ -27514,10 +28423,10 @@
         <v>041340</v>
       </c>
       <c r="S305" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T305" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U305" t="str">
         <v/>
@@ -27545,6 +28454,9 @@
       </c>
       <c r="AC305" t="str">
         <v/>
+      </c>
+      <c r="AD305" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="306">
@@ -27603,10 +28515,10 @@
         <v>041357</v>
       </c>
       <c r="S306" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T306" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U306" t="str">
         <v/>
@@ -27634,6 +28546,9 @@
       </c>
       <c r="AC306" t="str">
         <v/>
+      </c>
+      <c r="AD306" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="307">
@@ -27692,10 +28607,10 @@
         <v>-</v>
       </c>
       <c r="S307" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T307" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U307" t="str">
         <v/>
@@ -27723,6 +28638,9 @@
       </c>
       <c r="AC307" t="str">
         <v/>
+      </c>
+      <c r="AD307" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="308">
@@ -27781,10 +28699,10 @@
         <v>045119</v>
       </c>
       <c r="S308" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T308" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U308" t="str">
         <v/>
@@ -27812,6 +28730,9 @@
       </c>
       <c r="AC308" t="str">
         <v/>
+      </c>
+      <c r="AD308" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="309">
@@ -27870,10 +28791,10 @@
         <v>045126</v>
       </c>
       <c r="S309" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T309" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U309" t="str">
         <v/>
@@ -27901,6 +28822,9 @@
       </c>
       <c r="AC309" t="str">
         <v/>
+      </c>
+      <c r="AD309" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="310">
@@ -27959,10 +28883,10 @@
         <v>045133</v>
       </c>
       <c r="S310" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T310" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U310" t="str">
         <v/>
@@ -27990,6 +28914,9 @@
       </c>
       <c r="AC310" t="str">
         <v/>
+      </c>
+      <c r="AD310" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="311">
@@ -28048,10 +28975,10 @@
         <v>045140</v>
       </c>
       <c r="S311" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T311" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U311" t="str">
         <v/>
@@ -28079,6 +29006,9 @@
       </c>
       <c r="AC311" t="str">
         <v/>
+      </c>
+      <c r="AD311" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="312">
@@ -28137,10 +29067,10 @@
         <v>045157</v>
       </c>
       <c r="S312" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T312" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U312" t="str">
         <v/>
@@ -28168,6 +29098,9 @@
       </c>
       <c r="AC312" t="str">
         <v/>
+      </c>
+      <c r="AD312" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="313">
@@ -28226,10 +29159,10 @@
         <v>045164</v>
       </c>
       <c r="S313" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T313" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U313" t="str">
         <v/>
@@ -28257,6 +29190,9 @@
       </c>
       <c r="AC313" t="str">
         <v/>
+      </c>
+      <c r="AD313" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="314">
@@ -28315,10 +29251,10 @@
         <v>045171</v>
       </c>
       <c r="S314" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T314" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U314" t="str">
         <v/>
@@ -28346,6 +29282,9 @@
       </c>
       <c r="AC314" t="str">
         <v/>
+      </c>
+      <c r="AD314" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="315">
@@ -28404,10 +29343,10 @@
         <v>045188</v>
       </c>
       <c r="S315" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T315" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U315" t="str">
         <v/>
@@ -28435,6 +29374,9 @@
       </c>
       <c r="AC315" t="str">
         <v/>
+      </c>
+      <c r="AD315" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="316">
@@ -28493,10 +29435,10 @@
         <v>045195</v>
       </c>
       <c r="S316" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T316" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U316" t="str">
         <v/>
@@ -28524,6 +29466,9 @@
       </c>
       <c r="AC316" t="str">
         <v/>
+      </c>
+      <c r="AD316" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="317">
@@ -28582,10 +29527,10 @@
         <v>045201</v>
       </c>
       <c r="S317" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T317" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U317" t="str">
         <v/>
@@ -28613,6 +29558,9 @@
       </c>
       <c r="AC317" t="str">
         <v/>
+      </c>
+      <c r="AD317" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="318">
@@ -28671,10 +29619,10 @@
         <v>045218</v>
       </c>
       <c r="S318" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T318" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U318" t="str">
         <v/>
@@ -28702,6 +29650,9 @@
       </c>
       <c r="AC318" t="str">
         <v/>
+      </c>
+      <c r="AD318" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="319">
@@ -28760,10 +29711,10 @@
         <v>048066</v>
       </c>
       <c r="S319" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T319" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U319" t="str">
         <v/>
@@ -28791,6 +29742,9 @@
       </c>
       <c r="AC319" t="str">
         <v/>
+      </c>
+      <c r="AD319" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="320">
@@ -28849,10 +29803,10 @@
         <v>048073</v>
       </c>
       <c r="S320" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T320" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U320" t="str">
         <v/>
@@ -28880,6 +29834,9 @@
       </c>
       <c r="AC320" t="str">
         <v/>
+      </c>
+      <c r="AD320" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="321">
@@ -28938,10 +29895,10 @@
         <v>048080</v>
       </c>
       <c r="S321" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T321" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U321" t="str">
         <v/>
@@ -28969,6 +29926,9 @@
       </c>
       <c r="AC321" t="str">
         <v/>
+      </c>
+      <c r="AD321" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="322">
@@ -29027,10 +29987,10 @@
         <v>048097</v>
       </c>
       <c r="S322" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T322" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U322" t="str">
         <v/>
@@ -29058,6 +30018,9 @@
       </c>
       <c r="AC322" t="str">
         <v/>
+      </c>
+      <c r="AD322" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="323">
@@ -29116,10 +30079,10 @@
         <v>048103</v>
       </c>
       <c r="S323" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T323" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U323" t="str">
         <v/>
@@ -29147,6 +30110,9 @@
       </c>
       <c r="AC323" t="str">
         <v/>
+      </c>
+      <c r="AD323" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="324">
@@ -29205,10 +30171,10 @@
         <v>048110</v>
       </c>
       <c r="S324" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T324" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U324" t="str">
         <v/>
@@ -29236,6 +30202,9 @@
       </c>
       <c r="AC324" t="str">
         <v/>
+      </c>
+      <c r="AD324" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="325">
@@ -29294,10 +30263,10 @@
         <v>048127</v>
       </c>
       <c r="S325" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T325" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U325" t="str">
         <v/>
@@ -29325,6 +30294,9 @@
       </c>
       <c r="AC325" t="str">
         <v/>
+      </c>
+      <c r="AD325" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="326">
@@ -29383,10 +30355,10 @@
         <v>048134</v>
       </c>
       <c r="S326" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T326" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U326" t="str">
         <v/>
@@ -29414,6 +30386,9 @@
       </c>
       <c r="AC326" t="str">
         <v/>
+      </c>
+      <c r="AD326" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="327">
@@ -29472,10 +30447,10 @@
         <v>048141</v>
       </c>
       <c r="S327" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T327" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U327" t="str">
         <v/>
@@ -29503,6 +30478,9 @@
       </c>
       <c r="AC327" t="str">
         <v/>
+      </c>
+      <c r="AD327" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="328">
@@ -29561,10 +30539,10 @@
         <v>048158</v>
       </c>
       <c r="S328" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T328" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U328" t="str">
         <v/>
@@ -29592,6 +30570,9 @@
       </c>
       <c r="AC328" t="str">
         <v/>
+      </c>
+      <c r="AD328" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="329">
@@ -29650,10 +30631,10 @@
         <v>048165</v>
       </c>
       <c r="S329" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T329" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U329" t="str">
         <v/>
@@ -29681,6 +30662,9 @@
       </c>
       <c r="AC329" t="str">
         <v/>
+      </c>
+      <c r="AD329" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="330">
@@ -29739,10 +30723,10 @@
         <v>048172</v>
       </c>
       <c r="S330" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T330" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U330" t="str">
         <v/>
@@ -29770,6 +30754,9 @@
       </c>
       <c r="AC330" t="str">
         <v/>
+      </c>
+      <c r="AD330" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="331">
@@ -29828,10 +30815,10 @@
         <v/>
       </c>
       <c r="S331" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T331" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U331" t="str">
         <v/>
@@ -29859,6 +30846,9 @@
       </c>
       <c r="AC331" t="str">
         <v/>
+      </c>
+      <c r="AD331" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="332">
@@ -29917,10 +30907,10 @@
         <v/>
       </c>
       <c r="S332" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T332" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U332" t="str">
         <v/>
@@ -29948,6 +30938,9 @@
       </c>
       <c r="AC332" t="str">
         <v/>
+      </c>
+      <c r="AD332" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="333">
@@ -30006,10 +30999,10 @@
         <v/>
       </c>
       <c r="S333" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T333" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U333" t="str">
         <v/>
@@ -30037,6 +31030,9 @@
       </c>
       <c r="AC333" t="str">
         <v/>
+      </c>
+      <c r="AD333" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="334">
@@ -30095,10 +31091,10 @@
         <v/>
       </c>
       <c r="S334" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T334" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U334" t="str">
         <v/>
@@ -30126,6 +31122,9 @@
       </c>
       <c r="AC334" t="str">
         <v/>
+      </c>
+      <c r="AD334" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="335">
@@ -30184,10 +31183,10 @@
         <v/>
       </c>
       <c r="S335" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T335" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U335" t="str">
         <v/>
@@ -30215,6 +31214,9 @@
       </c>
       <c r="AC335" t="str">
         <v/>
+      </c>
+      <c r="AD335" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="336">
@@ -30273,10 +31275,10 @@
         <v/>
       </c>
       <c r="S336" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T336" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U336" t="str">
         <v/>
@@ -30304,6 +31306,9 @@
       </c>
       <c r="AC336" t="str">
         <v/>
+      </c>
+      <c r="AD336" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="337">
@@ -30362,10 +31367,10 @@
         <v/>
       </c>
       <c r="S337" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T337" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U337" t="str">
         <v/>
@@ -30393,6 +31398,9 @@
       </c>
       <c r="AC337" t="str">
         <v/>
+      </c>
+      <c r="AD337" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="338">
@@ -30451,10 +31459,10 @@
         <v>044495</v>
       </c>
       <c r="S338" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T338" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U338" t="str">
         <v/>
@@ -30482,6 +31490,9 @@
       </c>
       <c r="AC338" t="str">
         <v/>
+      </c>
+      <c r="AD338" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="339">
@@ -30540,10 +31551,10 @@
         <v>044501</v>
       </c>
       <c r="S339" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T339" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U339" t="str">
         <v/>
@@ -30571,6 +31582,9 @@
       </c>
       <c r="AC339" t="str">
         <v/>
+      </c>
+      <c r="AD339" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="340">
@@ -30629,10 +31643,10 @@
         <v>044518</v>
       </c>
       <c r="S340" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T340" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U340" t="str">
         <v/>
@@ -30660,6 +31674,9 @@
       </c>
       <c r="AC340" t="str">
         <v/>
+      </c>
+      <c r="AD340" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="341">
@@ -30718,10 +31735,10 @@
         <v>044525</v>
       </c>
       <c r="S341" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T341" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U341" t="str">
         <v/>
@@ -30749,6 +31766,9 @@
       </c>
       <c r="AC341" t="str">
         <v/>
+      </c>
+      <c r="AD341" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="342">
@@ -30807,10 +31827,10 @@
         <v>044532</v>
       </c>
       <c r="S342" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T342" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U342" t="str">
         <v/>
@@ -30838,6 +31858,9 @@
       </c>
       <c r="AC342" t="str">
         <v/>
+      </c>
+      <c r="AD342" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="343">
@@ -30896,10 +31919,10 @@
         <v>044549</v>
       </c>
       <c r="S343" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T343" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U343" t="str">
         <v/>
@@ -30927,6 +31950,9 @@
       </c>
       <c r="AC343" t="str">
         <v/>
+      </c>
+      <c r="AD343" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="344">
@@ -30985,10 +32011,10 @@
         <v>044556</v>
       </c>
       <c r="S344" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T344" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U344" t="str">
         <v/>
@@ -31016,6 +32042,9 @@
       </c>
       <c r="AC344" t="str">
         <v/>
+      </c>
+      <c r="AD344" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="345">
@@ -31074,10 +32103,10 @@
         <v>044563</v>
       </c>
       <c r="S345" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T345" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U345" t="str">
         <v/>
@@ -31105,6 +32134,9 @@
       </c>
       <c r="AC345" t="str">
         <v/>
+      </c>
+      <c r="AD345" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="346">
@@ -31163,10 +32195,10 @@
         <v>044570</v>
       </c>
       <c r="S346" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T346" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U346" t="str">
         <v/>
@@ -31194,6 +32226,9 @@
       </c>
       <c r="AC346" t="str">
         <v/>
+      </c>
+      <c r="AD346" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="347">
@@ -31252,10 +32287,10 @@
         <v>044587</v>
       </c>
       <c r="S347" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T347" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U347" t="str">
         <v/>
@@ -31283,6 +32318,9 @@
       </c>
       <c r="AC347" t="str">
         <v/>
+      </c>
+      <c r="AD347" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="348">
@@ -31341,10 +32379,10 @@
         <v>044594</v>
       </c>
       <c r="S348" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T348" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U348" t="str">
         <v/>
@@ -31372,6 +32410,9 @@
       </c>
       <c r="AC348" t="str">
         <v/>
+      </c>
+      <c r="AD348" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="349">
@@ -31430,10 +32471,10 @@
         <v>044600</v>
       </c>
       <c r="S349" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T349" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U349" t="str">
         <v/>
@@ -31461,6 +32502,9 @@
       </c>
       <c r="AC349" t="str">
         <v/>
+      </c>
+      <c r="AD349" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="350">
@@ -31519,10 +32563,10 @@
         <v>048233</v>
       </c>
       <c r="S350" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T350" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U350" t="str">
         <v/>
@@ -31550,6 +32594,9 @@
       </c>
       <c r="AC350" t="str">
         <v>20</v>
+      </c>
+      <c r="AD350" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="351">
@@ -31608,10 +32655,10 @@
         <v>048240</v>
       </c>
       <c r="S351" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T351" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U351" t="str">
         <v/>
@@ -31639,6 +32686,9 @@
       </c>
       <c r="AC351" t="str">
         <v>20</v>
+      </c>
+      <c r="AD351" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="352">
@@ -31697,10 +32747,10 @@
         <v>048257</v>
       </c>
       <c r="S352" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T352" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U352" t="str">
         <v/>
@@ -31728,6 +32778,9 @@
       </c>
       <c r="AC352" t="str">
         <v>-</v>
+      </c>
+      <c r="AD352" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="353">
@@ -31786,10 +32839,10 @@
         <v>048264</v>
       </c>
       <c r="S353" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T353" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U353" t="str">
         <v/>
@@ -31817,6 +32870,9 @@
       </c>
       <c r="AC353" t="str">
         <v>-</v>
+      </c>
+      <c r="AD353" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="354">
@@ -31875,10 +32931,10 @@
         <v>048271</v>
       </c>
       <c r="S354" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T354" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U354" t="str">
         <v/>
@@ -31906,6 +32962,9 @@
       </c>
       <c r="AC354" t="str">
         <v>-</v>
+      </c>
+      <c r="AD354" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="355">
@@ -31964,10 +33023,10 @@
         <v>037732</v>
       </c>
       <c r="S355" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T355" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U355" t="str">
         <v/>
@@ -31995,6 +33054,9 @@
       </c>
       <c r="AC355" t="str">
         <v/>
+      </c>
+      <c r="AD355" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="356">
@@ -32053,10 +33115,10 @@
         <v>037749</v>
       </c>
       <c r="S356" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T356" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U356" t="str">
         <v/>
@@ -32084,6 +33146,9 @@
       </c>
       <c r="AC356" t="str">
         <v/>
+      </c>
+      <c r="AD356" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="357">
@@ -32142,10 +33207,10 @@
         <v>046413</v>
       </c>
       <c r="S357" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T357" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U357" t="str">
         <v/>
@@ -32173,6 +33238,9 @@
       </c>
       <c r="AC357" t="str">
         <v/>
+      </c>
+      <c r="AD357" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="358">
@@ -32231,10 +33299,10 @@
         <v>046420</v>
       </c>
       <c r="S358" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T358" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U358" t="str">
         <v/>
@@ -32262,6 +33330,9 @@
       </c>
       <c r="AC358" t="str">
         <v/>
+      </c>
+      <c r="AD358" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="359">
@@ -32320,10 +33391,10 @@
         <v>046437</v>
       </c>
       <c r="S359" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T359" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U359" t="str">
         <v/>
@@ -32351,6 +33422,9 @@
       </c>
       <c r="AC359" t="str">
         <v/>
+      </c>
+      <c r="AD359" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="360">
@@ -32409,10 +33483,10 @@
         <v>046444</v>
       </c>
       <c r="S360" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T360" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U360" t="str">
         <v/>
@@ -32440,6 +33514,9 @@
       </c>
       <c r="AC360" t="str">
         <v/>
+      </c>
+      <c r="AD360" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="361">
@@ -32498,10 +33575,10 @@
         <v>046451</v>
       </c>
       <c r="S361" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T361" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U361" t="str">
         <v/>
@@ -32529,6 +33606,9 @@
       </c>
       <c r="AC361" t="str">
         <v/>
+      </c>
+      <c r="AD361" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="362">
@@ -32587,10 +33667,10 @@
         <v>046468</v>
       </c>
       <c r="S362" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T362" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U362" t="str">
         <v/>
@@ -32618,6 +33698,9 @@
       </c>
       <c r="AC362" t="str">
         <v/>
+      </c>
+      <c r="AD362" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="363">
@@ -32676,10 +33759,10 @@
         <v>046475</v>
       </c>
       <c r="S363" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T363" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U363" t="str">
         <v/>
@@ -32707,6 +33790,9 @@
       </c>
       <c r="AC363" t="str">
         <v/>
+      </c>
+      <c r="AD363" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="364">
@@ -32765,10 +33851,10 @@
         <v>046482</v>
       </c>
       <c r="S364" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T364" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U364" t="str">
         <v/>
@@ -32796,6 +33882,9 @@
       </c>
       <c r="AC364" t="str">
         <v/>
+      </c>
+      <c r="AD364" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="365">
@@ -32854,10 +33943,10 @@
         <v>046499</v>
       </c>
       <c r="S365" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T365" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U365" t="str">
         <v/>
@@ -32885,6 +33974,9 @@
       </c>
       <c r="AC365" t="str">
         <v/>
+      </c>
+      <c r="AD365" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="366">
@@ -32943,10 +34035,10 @@
         <v>046505</v>
       </c>
       <c r="S366" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T366" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U366" t="str">
         <v/>
@@ -32974,6 +34066,9 @@
       </c>
       <c r="AC366" t="str">
         <v/>
+      </c>
+      <c r="AD366" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="367">
@@ -33032,10 +34127,10 @@
         <v>046512</v>
       </c>
       <c r="S367" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T367" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U367" t="str">
         <v/>
@@ -33063,6 +34158,9 @@
       </c>
       <c r="AC367" t="str">
         <v/>
+      </c>
+      <c r="AD367" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="368">
@@ -33121,10 +34219,10 @@
         <v>046529</v>
       </c>
       <c r="S368" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T368" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U368" t="str">
         <v/>
@@ -33152,6 +34250,9 @@
       </c>
       <c r="AC368" t="str">
         <v/>
+      </c>
+      <c r="AD368" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="369">
@@ -33210,10 +34311,10 @@
         <v>046536</v>
       </c>
       <c r="S369" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T369" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U369" t="str">
         <v/>
@@ -33241,6 +34342,9 @@
       </c>
       <c r="AC369" t="str">
         <v/>
+      </c>
+      <c r="AD369" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="370">
@@ -33299,10 +34403,10 @@
         <v>046543</v>
       </c>
       <c r="S370" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T370" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U370" t="str">
         <v/>
@@ -33330,6 +34434,9 @@
       </c>
       <c r="AC370" t="str">
         <v/>
+      </c>
+      <c r="AD370" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="371">
@@ -33388,10 +34495,10 @@
         <v>027757</v>
       </c>
       <c r="S371" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T371" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U371" t="str">
         <v/>
@@ -33419,6 +34526,9 @@
       </c>
       <c r="AC371" t="str">
         <v/>
+      </c>
+      <c r="AD371" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="372">
@@ -33477,10 +34587,10 @@
         <v>027764</v>
       </c>
       <c r="S372" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T372" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U372" t="str">
         <v/>
@@ -33508,6 +34618,9 @@
       </c>
       <c r="AC372" t="str">
         <v/>
+      </c>
+      <c r="AD372" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="373">
@@ -33566,10 +34679,10 @@
         <v>039163</v>
       </c>
       <c r="S373" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T373" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U373" t="str">
         <v/>
@@ -33597,6 +34710,9 @@
       </c>
       <c r="AC373" t="str">
         <v/>
+      </c>
+      <c r="AD373" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="374">
@@ -33655,10 +34771,10 @@
         <v>039187</v>
       </c>
       <c r="S374" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T374" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U374" t="str">
         <v/>
@@ -33686,6 +34802,9 @@
       </c>
       <c r="AC374" t="str">
         <v/>
+      </c>
+      <c r="AD374" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="375">
@@ -33744,10 +34863,10 @@
         <v>049445</v>
       </c>
       <c r="S375" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T375" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U375" t="str">
         <v/>
@@ -33775,6 +34894,9 @@
       </c>
       <c r="AC375" t="str">
         <v/>
+      </c>
+      <c r="AD375" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="376">
@@ -33833,10 +34955,10 @@
         <v>049452</v>
       </c>
       <c r="S376" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T376" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U376" t="str">
         <v/>
@@ -33864,6 +34986,9 @@
       </c>
       <c r="AC376" t="str">
         <v/>
+      </c>
+      <c r="AD376" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="377">
@@ -33922,10 +35047,10 @@
         <v>049469</v>
       </c>
       <c r="S377" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T377" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U377" t="str">
         <v/>
@@ -33953,6 +35078,9 @@
       </c>
       <c r="AC377" t="str">
         <v/>
+      </c>
+      <c r="AD377" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="378">
@@ -34011,10 +35139,10 @@
         <v>049476</v>
       </c>
       <c r="S378" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T378" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U378" t="str">
         <v/>
@@ -34042,6 +35170,9 @@
       </c>
       <c r="AC378" t="str">
         <v/>
+      </c>
+      <c r="AD378" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="379">
@@ -34100,10 +35231,10 @@
         <v>049483</v>
       </c>
       <c r="S379" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T379" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U379" t="str">
         <v/>
@@ -34131,6 +35262,9 @@
       </c>
       <c r="AC379" t="str">
         <v/>
+      </c>
+      <c r="AD379" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="380">
@@ -34189,10 +35323,10 @@
         <v>049490</v>
       </c>
       <c r="S380" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T380" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U380" t="str">
         <v/>
@@ -34220,6 +35354,9 @@
       </c>
       <c r="AC380" t="str">
         <v/>
+      </c>
+      <c r="AD380" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="381">
@@ -34278,10 +35415,10 @@
         <v>049506</v>
       </c>
       <c r="S381" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T381" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U381" t="str">
         <v/>
@@ -34309,6 +35446,9 @@
       </c>
       <c r="AC381" t="str">
         <v/>
+      </c>
+      <c r="AD381" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="382">
@@ -34367,10 +35507,10 @@
         <v>049513</v>
       </c>
       <c r="S382" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T382" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U382" t="str">
         <v/>
@@ -34398,6 +35538,9 @@
       </c>
       <c r="AC382" t="str">
         <v/>
+      </c>
+      <c r="AD382" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="383">
@@ -34456,10 +35599,10 @@
         <v>049520</v>
       </c>
       <c r="S383" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T383" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U383" t="str">
         <v/>
@@ -34487,6 +35630,9 @@
       </c>
       <c r="AC383" t="str">
         <v/>
+      </c>
+      <c r="AD383" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="384">
@@ -34545,10 +35691,10 @@
         <v>049537</v>
       </c>
       <c r="S384" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T384" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U384" t="str">
         <v/>
@@ -34576,6 +35722,9 @@
       </c>
       <c r="AC384" t="str">
         <v/>
+      </c>
+      <c r="AD384" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="385">
@@ -34634,10 +35783,10 @@
         <v>049544</v>
       </c>
       <c r="S385" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T385" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U385" t="str">
         <v/>
@@ -34665,6 +35814,9 @@
       </c>
       <c r="AC385" t="str">
         <v/>
+      </c>
+      <c r="AD385" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="386">
@@ -34723,10 +35875,10 @@
         <v/>
       </c>
       <c r="S386" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T386" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U386" t="str">
         <v/>
@@ -34754,6 +35906,9 @@
       </c>
       <c r="AC386" t="str">
         <v/>
+      </c>
+      <c r="AD386" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="387">
@@ -34812,10 +35967,10 @@
         <v/>
       </c>
       <c r="S387" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T387" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U387" t="str">
         <v/>
@@ -34843,6 +35998,9 @@
       </c>
       <c r="AC387" t="str">
         <v/>
+      </c>
+      <c r="AD387" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="388">
@@ -34901,10 +36059,10 @@
         <v/>
       </c>
       <c r="S388" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T388" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U388" t="str">
         <v/>
@@ -34932,6 +36090,9 @@
       </c>
       <c r="AC388" t="str">
         <v/>
+      </c>
+      <c r="AD388" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="389">
@@ -34990,10 +36151,10 @@
         <v/>
       </c>
       <c r="S389" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T389" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U389" t="str">
         <v/>
@@ -35021,6 +36182,9 @@
       </c>
       <c r="AC389" t="str">
         <v/>
+      </c>
+      <c r="AD389" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="390">
@@ -35079,10 +36243,10 @@
         <v/>
       </c>
       <c r="S390" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T390" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U390" t="str">
         <v/>
@@ -35110,6 +36274,9 @@
       </c>
       <c r="AC390" t="str">
         <v/>
+      </c>
+      <c r="AD390" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="391">
@@ -35168,10 +36335,10 @@
         <v/>
       </c>
       <c r="S391" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T391" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U391" t="str">
         <v/>
@@ -35199,6 +36366,9 @@
       </c>
       <c r="AC391" t="str">
         <v/>
+      </c>
+      <c r="AD391" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="392">
@@ -35257,10 +36427,10 @@
         <v/>
       </c>
       <c r="S392" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T392" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U392" t="str">
         <v/>
@@ -35288,6 +36458,9 @@
       </c>
       <c r="AC392" t="str">
         <v/>
+      </c>
+      <c r="AD392" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="393">
@@ -35346,10 +36519,10 @@
         <v/>
       </c>
       <c r="S393" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T393" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U393" t="str">
         <v/>
@@ -35377,6 +36550,9 @@
       </c>
       <c r="AC393" t="str">
         <v/>
+      </c>
+      <c r="AD393" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="394">
@@ -35435,10 +36611,10 @@
         <v/>
       </c>
       <c r="S394" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T394" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U394" t="str">
         <v/>
@@ -35466,6 +36642,9 @@
       </c>
       <c r="AC394" t="str">
         <v/>
+      </c>
+      <c r="AD394" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="395">
@@ -35524,10 +36703,10 @@
         <v/>
       </c>
       <c r="S395" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T395" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U395" t="str">
         <v/>
@@ -35555,6 +36734,9 @@
       </c>
       <c r="AC395" t="str">
         <v/>
+      </c>
+      <c r="AD395" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="396">
@@ -35613,10 +36795,10 @@
         <v/>
       </c>
       <c r="S396" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T396" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U396" t="str">
         <v/>
@@ -35644,6 +36826,9 @@
       </c>
       <c r="AC396" t="str">
         <v/>
+      </c>
+      <c r="AD396" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="397">
@@ -35702,10 +36887,10 @@
         <v/>
       </c>
       <c r="S397" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T397" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U397" t="str">
         <v/>
@@ -35733,6 +36918,9 @@
       </c>
       <c r="AC397" t="str">
         <v/>
+      </c>
+      <c r="AD397" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="398">
@@ -35791,10 +36979,10 @@
         <v/>
       </c>
       <c r="S398" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T398" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U398" t="str">
         <v/>
@@ -35822,6 +37010,9 @@
       </c>
       <c r="AC398" t="str">
         <v/>
+      </c>
+      <c r="AD398" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="399">
@@ -35880,10 +37071,10 @@
         <v/>
       </c>
       <c r="S399" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T399" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U399" t="str">
         <v/>
@@ -35911,6 +37102,9 @@
       </c>
       <c r="AC399" t="str">
         <v/>
+      </c>
+      <c r="AD399" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="400">
@@ -35969,10 +37163,10 @@
         <v/>
       </c>
       <c r="S400" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T400" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U400" t="str">
         <v/>
@@ -36000,6 +37194,9 @@
       </c>
       <c r="AC400" t="str">
         <v/>
+      </c>
+      <c r="AD400" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="401">
@@ -36058,10 +37255,10 @@
         <v/>
       </c>
       <c r="S401" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T401" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U401" t="str">
         <v/>
@@ -36089,6 +37286,9 @@
       </c>
       <c r="AC401" t="str">
         <v/>
+      </c>
+      <c r="AD401" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="402">
@@ -36147,10 +37347,10 @@
         <v/>
       </c>
       <c r="S402" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T402" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U402" t="str">
         <v/>
@@ -36178,6 +37378,9 @@
       </c>
       <c r="AC402" t="str">
         <v/>
+      </c>
+      <c r="AD402" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="403">
@@ -36236,10 +37439,10 @@
         <v/>
       </c>
       <c r="S403" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T403" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U403" t="str">
         <v/>
@@ -36267,6 +37470,9 @@
       </c>
       <c r="AC403" t="str">
         <v/>
+      </c>
+      <c r="AD403" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="404">
@@ -36325,10 +37531,10 @@
         <v/>
       </c>
       <c r="S404" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T404" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U404" t="str">
         <v/>
@@ -36356,6 +37562,9 @@
       </c>
       <c r="AC404" t="str">
         <v/>
+      </c>
+      <c r="AD404" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="405">
@@ -36414,10 +37623,10 @@
         <v/>
       </c>
       <c r="S405" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="T405" t="str">
-        <v>2026-04-09 12:52:05</v>
+        <v>2026-04-10 00:51:20</v>
       </c>
       <c r="U405" t="str">
         <v/>
@@ -36445,6 +37654,9 @@
       </c>
       <c r="AC405" t="str">
         <v/>
+      </c>
+      <c r="AD405" t="str">
+        <v>spinning</v>
       </c>
     </row>
     <row r="406">

--- a/GearSage-client/rate/excel/spinning_reel_detail.xlsx
+++ b/GearSage-client/rate/excel/spinning_reel_detail.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK723"/>
+  <dimension ref="A1:AN723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -634,6 +634,21 @@
           <t>variant_description</t>
         </is>
       </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>player_environment</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>is_handle_double</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">

--- a/GearSage-client/rate/excel/spinning_reel_detail.xlsx
+++ b/GearSage-client/rate/excel/spinning_reel_detail.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -401,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR713"/>
+  <dimension ref="A1:AR715"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -95945,9 +95941,277 @@
         <v/>
       </c>
     </row>
+    <row r="714">
+      <c r="A714" t="str">
+        <v>MRED50002</v>
+      </c>
+      <c r="B714" t="str">
+        <v>MRE5002</v>
+      </c>
+      <c r="C714" t="str">
+        <v>LIN258HM</v>
+      </c>
+      <c r="D714" t="str">
+        <v>6.0</v>
+      </c>
+      <c r="E714" t="str">
+        <v/>
+      </c>
+      <c r="F714" t="str">
+        <v>7.0</v>
+      </c>
+      <c r="G714" t="str">
+        <v>248</v>
+      </c>
+      <c r="H714" t="str">
+        <v/>
+      </c>
+      <c r="I714" t="str">
+        <v/>
+      </c>
+      <c r="J714" t="str">
+        <v/>
+      </c>
+      <c r="K714" t="str">
+        <v>6lb./210m / 8lb/150m</v>
+      </c>
+      <c r="L714" t="str">
+        <v/>
+      </c>
+      <c r="M714" t="str">
+        <v/>
+      </c>
+      <c r="N714" t="str">
+        <v/>
+      </c>
+      <c r="O714" t="str">
+        <v>91</v>
+      </c>
+      <c r="P714" t="str">
+        <v/>
+      </c>
+      <c r="Q714" t="str">
+        <v>12/1</v>
+      </c>
+      <c r="R714" t="str">
+        <v>铝</v>
+      </c>
+      <c r="S714" t="str">
+        <v/>
+      </c>
+      <c r="T714" t="str">
+        <v/>
+      </c>
+      <c r="U714" t="str">
+        <v/>
+      </c>
+      <c r="V714" t="str">
+        <v/>
+      </c>
+      <c r="W714" t="str">
+        <v/>
+      </c>
+      <c r="X714" t="str">
+        <v>¥55,000</v>
+      </c>
+      <c r="Y714" t="str">
+        <v/>
+      </c>
+      <c r="Z714" t="str">
+        <v>2026-04-21T12:02:55.901Z</v>
+      </c>
+      <c r="AA714" t="str">
+        <v>2026-04-21T12:02:55.901Z</v>
+      </c>
+      <c r="AB714" t="str">
+        <v/>
+      </c>
+      <c r="AC714" t="str">
+        <v/>
+      </c>
+      <c r="AD714" t="str">
+        <v/>
+      </c>
+      <c r="AE714" t="str">
+        <v/>
+      </c>
+      <c r="AF714" t="str">
+        <v>重装,高刚性,精细</v>
+      </c>
+      <c r="AG714" t="str">
+        <v>约 3g+</v>
+      </c>
+      <c r="AH714" t="str">
+        <v/>
+      </c>
+      <c r="AI714" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AJ714" t="str">
+        <v/>
+      </c>
+      <c r="AK714" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="AL714" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM714" t="str">
+        <v/>
+      </c>
+      <c r="AN714" t="str">
+        <v>カヴァーフィネスゲームをはじめ、ラフウォーターでのバスボートゲームなど、激しい釣りに耐えうるタフな野外戦用スピニングがLIN258HMである。アルミメタル製のドライブギアは、超高精度マシンカットで「一個一個」「一歯一歯」の工程で歯面の最終仕上げを施すという念の入れ様。噛み合うピニオンギアのデジタル数値に、ドライブギアをミクロンの精度で適合させるという極みの技。リンのシームレスなシルキードライブは、これに加えてギアを支えるハウジングもたわみの発生しない高精度・高剛性のアルミメタル製なのだ。勘合部さえもすべて「一個一個」ミクロンの精度で削り出す。クラフツマンの魂を込めたこの丹念な工程こそが、リンのまるでガタのない強靭な駆動部分を造り出している。リンのハンドルを回せば「噛み合い接触」の感触よりも「スベリ接触」の感触が強めに出ていることが感じていただけると思う。このシルキーな噛み合いこそが、回せば瞬時に立ち上がるロスのないハイパワーと、高次元の感度伝達性を生み出すのだ。なお、メカハウジングとして、可動部には最新の磁性流体シールドで保護。極限の遠心力低減化を追求したローター部分はグラファイトコンポジット製。スプールも限界まで肉抜きされたハニカム構造で耐久性を両立。ハンドルは、最新のメカニカルパワーアシストを施し、もはやワンランク上の機種として使用可能なオーバーパワースペックを持つリールなのだ。世界記録バスのパワーランに耐え得るために、Ｍドラグシステムはスムーズで耐久性・耐力のある高荷重カーボンの多重構造を採用。卓越した追撃性能を具現化したLIN258HMは、バスフィッシングはもちろんのこと、シーバスゲームやノースエリアの巨大鱒族を相手にも存分に威力を発揮。その名のとおり、凛として戦うモンスタースペックのスピニングリールなのだ。 The LIN258HM is a battle reel made to withstand tough and intense fishing. The aluminum gear drive is finished off by carefully machining each gear tooth with extreme precision. The extreme engineering skills employed allow the drive gear to be fitted to the pinion gear with only microns to spare. The seamless silky drive of the LIN is made of high-precision high-rigidity aluminum, which prevents deflection of the supporting gear housing. The precision manufacturing process combined with the soul of the craftsmen who assemble the product are what make the LIN what it is. This silky gear engagement of the LIN is what creates its sensitivity and creates the high power that engages immediately when turning the handle. Furthermore, in the mechanical housing, the moving parts are protected with the latest magnetic fluid shield. The rotor is made from lightweight graphite composites to reduce centrifugal force and increase stability. The spool also has also undergone weight reduction, implementing a durable honeycomb construction. The mechanical power assist of the handle gives it power equal to higher spec'd models. In order to withstand the power of world record size bass, the M drag system is incorporated with its multiple structured, smooth, durable, heavyweight carbon. The LIN258HM is a powerful spinning reel that shows excellent performance when dealing with bass, sea bass, and large trout species.</v>
+      </c>
+      <c r="AO714" t="str">
+        <v>Cover / 精细重装</v>
+      </c>
+      <c r="AP714" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ714" t="str">
+        <v/>
+      </c>
+      <c r="AR714" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="str">
+        <v>MRED50003</v>
+      </c>
+      <c r="B715" t="str">
+        <v>MRE5003</v>
+      </c>
+      <c r="C715" t="str">
+        <v>RC-IDATEN 256</v>
+      </c>
+      <c r="D715" t="str">
+        <v>5.66</v>
+      </c>
+      <c r="E715" t="str">
+        <v/>
+      </c>
+      <c r="F715" t="str">
+        <v>3.0</v>
+      </c>
+      <c r="G715" t="str">
+        <v>215</v>
+      </c>
+      <c r="H715" t="str">
+        <v/>
+      </c>
+      <c r="I715" t="str">
+        <v/>
+      </c>
+      <c r="J715" t="str">
+        <v/>
+      </c>
+      <c r="K715" t="str">
+        <v>4lb./190m / 5lb/150m</v>
+      </c>
+      <c r="L715" t="str">
+        <v/>
+      </c>
+      <c r="M715" t="str">
+        <v/>
+      </c>
+      <c r="N715" t="str">
+        <v/>
+      </c>
+      <c r="O715" t="str">
+        <v>84</v>
+      </c>
+      <c r="P715" t="str">
+        <v/>
+      </c>
+      <c r="Q715" t="str">
+        <v>7/1</v>
+      </c>
+      <c r="R715" t="str">
+        <v>铝</v>
+      </c>
+      <c r="S715" t="str">
+        <v/>
+      </c>
+      <c r="T715" t="str">
+        <v/>
+      </c>
+      <c r="U715" t="str">
+        <v/>
+      </c>
+      <c r="V715" t="str">
+        <v/>
+      </c>
+      <c r="W715" t="str">
+        <v/>
+      </c>
+      <c r="X715" t="str">
+        <v>¥59,800</v>
+      </c>
+      <c r="Y715" t="str">
+        <v/>
+      </c>
+      <c r="Z715" t="str">
+        <v>2026-04-21T12:02:56.380Z</v>
+      </c>
+      <c r="AA715" t="str">
+        <v>2026-04-21T12:02:56.380Z</v>
+      </c>
+      <c r="AB715" t="str">
+        <v/>
+      </c>
+      <c r="AC715" t="str">
+        <v/>
+      </c>
+      <c r="AD715" t="str">
+        <v/>
+      </c>
+      <c r="AE715" t="str">
+        <v/>
+      </c>
+      <c r="AF715" t="str">
+        <v>高速,精细,泛用</v>
+      </c>
+      <c r="AG715" t="str">
+        <v>约 2g+</v>
+      </c>
+      <c r="AH715" t="str">
+        <v/>
+      </c>
+      <c r="AI715" t="str">
+        <v>单摇臂</v>
+      </c>
+      <c r="AJ715" t="str">
+        <v/>
+      </c>
+      <c r="AK715" t="str">
+        <v>spinning</v>
+      </c>
+      <c r="AL715" t="str">
+        <v>0</v>
+      </c>
+      <c r="AM715" t="str">
+        <v/>
+      </c>
+      <c r="AN715" t="str">
+        <v>「レーシングコンディション256」の軽量コンセプトとパッケージングレイアウトを踏襲し、ハンドル一回転におけるローター回転を高速化。ハンドル一巻きのライン巻き上げ量を大幅にアップした高速リールが、「IDATENプロジェクト」の最新形態として、遂に具現化。ハイスピードスピニングリールで痩せがちだった巻き上げトルクは、IDATEN256が過去のものとしています。「スピード」と「パワー」、この相反する要素の最大公約数にジャストミートさせた新たなIDATENが、効率よく釣り勝つためのハイテンポなフィネスゲームを展開します。 RC-IDATEN 256 inherits the Racing Condition 256 model’s lightweight concept, while at the same time delivering faster rotor rotation per handle turn.RC-IDATEN 256 has been tuned for blazing speed without stripping away underlying power, bringing a new standard of high-speed gearing and power. Increased retrieve speed without the loss of lightness or power: this is the latest core incarnation of the IDATEN reel project.Experience the perfect combination of speed and power with the new IDATEN 256. * The photograph is a prototype もはやこれ以上はない堅牢さと軽量化を高次元で両立させた、メガバス独自のメタル削り出し構造による「ハイメタル・ハニカムスプール」は、「磁性流体シールドシステム」の開発によって、スピニングリールにおける理想的なヘッドバランスを実現。その超軽量マイクロボディが発揮してしまう、およそ似合わないハイパワーは、究極のフィネスアプローチでレコードフィッシュと真っ向からわたり合うためのエクストリームなスペック。</v>
+      </c>
+      <c r="AO715" t="str">
+        <v>快节奏精细</v>
+      </c>
+      <c r="AP715" t="str">
+        <v>0</v>
+      </c>
+      <c r="AQ715" t="str">
+        <v/>
+      </c>
+      <c r="AR715" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AR713"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AR715"/>
   </ignoredErrors>
 </worksheet>
 </file>